--- a/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9631F86-588E-4B19-8370-AB9931099652}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740FE4BC-0202-4EEF-87FE-F1748AC77ED2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -6211,22 +6211,30 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>56</v>
+      </c>
+      <c r="D8" s="111">
+        <v>21</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
-        <f>C8-G8</f>
-        <v>0</v>
+        <f>C8+E8-G8</f>
+        <v>55</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
-      <c r="L8" s="112"/>
+      <c r="L8" s="112">
+        <v>1</v>
+      </c>
       <c r="M8" s="112"/>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
@@ -6234,7 +6242,7 @@
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -6243,15 +6251,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -6286,15 +6294,17 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>106</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
       <c r="G9" s="78"/>
       <c r="H9" s="79"/>
       <c r="I9" s="78">
-        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <f>C9+E9-G9</f>
+        <v>106</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -6326,7 +6336,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -6361,15 +6371,17 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>116</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
       <c r="G10" s="76"/>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" ref="I9:J59" si="4">C10-G10</f>
+        <v>116</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -6401,7 +6413,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2784</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -6436,7 +6448,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>14</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -6444,7 +6458,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -6476,7 +6490,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -6511,7 +6525,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="110">
+        <v>6</v>
+      </c>
       <c r="D12" s="111"/>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
@@ -6519,7 +6535,7 @@
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
@@ -6551,7 +6567,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -6586,47 +6602,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3839</v>
+      </c>
+      <c r="D13" s="114">
+        <v>21</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>35</v>
+      </c>
+      <c r="H13" s="79">
+        <v>30</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3804</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>8</v>
+      </c>
+      <c r="M13" s="121">
+        <v>4</v>
+      </c>
+      <c r="N13" s="121">
+        <v>6</v>
+      </c>
+      <c r="O13" s="121">
+        <v>4</v>
+      </c>
+      <c r="P13" s="121">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>22</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>91287</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -6668,19 +6704,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>4</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -6708,7 +6748,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -6743,7 +6783,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>3</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -6751,7 +6793,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -6783,7 +6825,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -6818,7 +6860,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>2</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -6826,7 +6870,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -6858,7 +6902,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -6893,7 +6937,9 @@
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="110"/>
+      <c r="C17" s="110">
+        <v>1</v>
+      </c>
       <c r="D17" s="111"/>
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
@@ -6901,7 +6947,7 @@
       <c r="H17" s="73"/>
       <c r="I17" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="77">
         <f t="shared" si="4"/>
@@ -6933,7 +6979,7 @@
       </c>
       <c r="W17" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X17" s="27"/>
       <c r="AL17" s="12"/>
@@ -6968,7 +7014,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -6976,7 +7024,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -7008,7 +7056,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -7118,19 +7166,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -7158,7 +7210,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -7193,19 +7245,23 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111">
+        <v>16</v>
+      </c>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
       <c r="G21" s="76"/>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K21" s="41"/>
       <c r="L21" s="112"/>
@@ -7233,7 +7289,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -7268,7 +7324,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>4</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -7276,7 +7334,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -7308,7 +7366,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -7343,19 +7401,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -7383,7 +7445,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -7425,19 +7487,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -7465,7 +7531,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -7507,7 +7573,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>11</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -7515,7 +7583,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -7547,7 +7615,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -7582,19 +7650,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>41</v>
+      </c>
+      <c r="D26" s="111">
+        <v>23</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -7622,7 +7694,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -7638,47 +7710,61 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>7</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="73"/>
+      <c r="G27" s="76">
+        <v>6</v>
+      </c>
+      <c r="H27" s="73">
+        <v>12</v>
+      </c>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K27" s="42"/>
-      <c r="L27" s="112"/>
+      <c r="L27" s="112">
+        <v>1</v>
+      </c>
       <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
+      <c r="N27" s="112">
+        <v>3</v>
+      </c>
+      <c r="O27" s="112">
+        <v>12</v>
+      </c>
+      <c r="P27" s="112">
+        <v>2</v>
+      </c>
       <c r="Q27" s="120"/>
       <c r="R27" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S27" s="124">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T27" s="42"/>
       <c r="U27" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V27" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W27" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -7697,7 +7783,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -7705,7 +7793,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="4"/>
@@ -7737,7 +7825,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -7756,47 +7844,63 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="111"/>
+      <c r="C29" s="110">
+        <v>57</v>
+      </c>
+      <c r="D29" s="111">
+        <v>12</v>
+      </c>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="76">
+        <v>7</v>
+      </c>
+      <c r="H29" s="73">
+        <v>12</v>
+      </c>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
       <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="N29" s="112">
+        <v>3</v>
+      </c>
+      <c r="O29" s="112">
+        <v>14</v>
+      </c>
+      <c r="P29" s="112">
+        <v>3</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -7815,7 +7919,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
+      <c r="C30" s="110">
+        <v>69</v>
+      </c>
       <c r="D30" s="111"/>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
@@ -7823,7 +7929,7 @@
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
@@ -7855,7 +7961,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1656</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -7867,15 +7973,19 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>43</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -7884,13 +7994,15 @@
       <c r="K31" s="41"/>
       <c r="L31" s="112"/>
       <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
+      <c r="N31" s="112">
+        <v>1</v>
+      </c>
       <c r="O31" s="112"/>
       <c r="P31" s="112"/>
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="7"/>
@@ -7899,15 +8011,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -7919,7 +8031,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -7927,7 +8041,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="4"/>
@@ -7959,7 +8073,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -7971,7 +8085,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>5</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -7979,7 +8095,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -8011,7 +8127,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -8023,7 +8139,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>5</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -8031,7 +8149,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="4"/>
@@ -8063,7 +8181,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -8075,22 +8193,30 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>133</v>
+      </c>
+      <c r="D35" s="111">
+        <v>5</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>1</v>
+      </c>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
@@ -8098,7 +8224,7 @@
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -8107,15 +8233,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3173</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -8179,7 +8305,9 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>2</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
@@ -8187,7 +8315,7 @@
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="77">
         <f t="shared" si="4"/>
@@ -8219,7 +8347,7 @@
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X37" s="27"/>
     </row>
@@ -8231,30 +8359,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4811</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>108</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4703</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>71</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>2</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>35</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -8263,15 +8403,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>28220</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -8283,7 +8423,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>7</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -8291,7 +8433,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="4"/>
@@ -8323,7 +8465,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -8335,7 +8477,9 @@
       <c r="B40" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="116">
+        <v>4</v>
+      </c>
       <c r="D40" s="117"/>
       <c r="E40" s="118"/>
       <c r="F40" s="118"/>
@@ -8343,7 +8487,7 @@
       <c r="H40" s="80"/>
       <c r="I40" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="77">
         <f t="shared" si="4"/>
@@ -8375,7 +8519,7 @@
       </c>
       <c r="W40" s="137">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X40" s="92"/>
     </row>
@@ -8387,15 +8531,19 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
+      <c r="C41" s="146">
+        <v>396</v>
+      </c>
       <c r="D41" s="147"/>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>72</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
@@ -8404,13 +8552,17 @@
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
-      <c r="N41" s="154"/>
+      <c r="N41" s="154">
+        <v>70</v>
+      </c>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>2</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="7"/>
@@ -8419,15 +8571,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1728</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7776</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -8439,30 +8591,42 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="164"/>
+      <c r="C42" s="163">
+        <v>1133</v>
+      </c>
+      <c r="D42" s="164">
+        <v>9</v>
+      </c>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>33</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>3</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>13</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>17</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -8471,15 +8635,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>13209</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -8534,30 +8698,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
+      <c r="C44" s="113">
+        <v>37601</v>
+      </c>
       <c r="D44" s="114"/>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1465</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>36136</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>644</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>339</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>482</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -8566,15 +8740,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>8790</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>216816</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -8630,7 +8804,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>3</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -8638,7 +8814,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="4"/>
@@ -8670,7 +8846,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -8734,22 +8910,30 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2847</v>
+      </c>
+      <c r="D48" s="142">
+        <v>4</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
-      <c r="G48" s="143"/>
+      <c r="G48" s="143">
+        <v>5</v>
+      </c>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="51"/>
-      <c r="L48" s="121"/>
+      <c r="L48" s="121">
+        <v>5</v>
+      </c>
       <c r="M48" s="121"/>
       <c r="N48" s="121"/>
       <c r="O48" s="121"/>
@@ -8757,7 +8941,7 @@
       <c r="Q48" s="122"/>
       <c r="R48" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S48" s="144">
         <f t="shared" si="7"/>
@@ -8766,15 +8950,15 @@
       <c r="T48" s="51"/>
       <c r="U48" s="131">
         <f>L48*6+N48*6+P48*6</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V48" s="135">
         <f>U48/6</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>17056</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -8786,7 +8970,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -8794,7 +8980,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -8826,7 +9012,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -8838,7 +9024,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -8846,7 +9034,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -8878,7 +9066,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -8942,7 +9130,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -8950,7 +9140,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -8982,7 +9172,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -8994,7 +9184,9 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>2</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
@@ -9002,7 +9194,7 @@
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="77">
         <f t="shared" si="4"/>
@@ -9034,7 +9226,7 @@
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X53" s="27"/>
     </row>
@@ -9046,7 +9238,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>14</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -9054,7 +9248,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -9086,7 +9280,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -9301,11 +9495,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>51444</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -9314,65 +9508,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1734</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>49710</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1734</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>12816</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
+        <v>1734</v>
       </c>
       <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>393104</v>
       </c>
       <c r="X60" s="45"/>
     </row>

--- a/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740FE4BC-0202-4EEF-87FE-F1748AC77ED2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18299A1D-4F90-4F55-A8AB-7E831F1950F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
     <sheet name="04,01" sheetId="106" r:id="rId2"/>
-    <sheet name="04,02" sheetId="108" r:id="rId3"/>
-    <sheet name="04,03" sheetId="107" r:id="rId4"/>
-    <sheet name="04,04" sheetId="109" r:id="rId5"/>
-    <sheet name="04,06" sheetId="110" r:id="rId6"/>
+    <sheet name="04,06" sheetId="110" r:id="rId3"/>
+    <sheet name="04,07" sheetId="108" r:id="rId4"/>
+    <sheet name="04,08" sheetId="107" r:id="rId5"/>
+    <sheet name="04,09" sheetId="109" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'04,01'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'04,02'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'04,03'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'04,04'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'04,06'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'04,06'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'04,07'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'04,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'04,09'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -221,6 +221,92 @@
     <author>User</author>
   </authors>
   <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{D87743D1-D5D0-4C4F-9684-970554587078}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{ABBCB3A3-AFF6-46E3-A1E0-338068DBBB30}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{C1184CB8-68F5-4E30-9BDA-A6C0AF698C4E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
     <comment ref="U5" authorId="0" shapeId="0" xr:uid="{8CC18E23-3D77-4DC5-A5D8-90BF6624E913}">
       <text>
         <r>
@@ -301,7 +387,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
@@ -387,7 +473,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
@@ -445,92 +531,6 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{D6E0B6C5-E243-4A03-895E-B92ABAA550F1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Ending Inventory
-Bottle Per Case</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>User</author>
-  </authors>
-  <commentList>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{D87743D1-D5D0-4C4F-9684-970554587078}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Inventory 
-Bottle Per Case
-All Route</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{ABBCB3A3-AFF6-46E3-A1E0-338068DBBB30}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Inventory
-Per Case</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{C1184CB8-68F5-4E30-9BDA-A6C0AF698C4E}">
       <text>
         <r>
           <rPr>
@@ -6380,7 +6380,7 @@
       <c r="G10" s="76"/>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
-        <f t="shared" ref="I9:J59" si="4">C10-G10</f>
+        <f t="shared" ref="I10:J59" si="4">C10-G10</f>
         <v>116</v>
       </c>
       <c r="J10" s="95">
@@ -10004,7 +10004,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F18521-30C6-4E9C-952F-E7D2A7665E71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DCBFCF-8FDE-4A25-9852-A6618DD949A0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10014,7 +10014,7 @@
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" customWidth="1"/>
@@ -10054,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="195">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="Q1" s="196"/>
       <c r="R1" s="196"/>
@@ -10137,7 +10137,7 @@
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="186" t="s">
+      <c r="F5" s="189" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="204"/>
@@ -10308,19 +10308,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>53</v>
+      </c>
+      <c r="D8" s="111">
+        <v>21</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -10348,7 +10352,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1293</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -10383,7 +10387,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>106</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -10391,7 +10397,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -10423,7 +10429,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2544</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -10458,7 +10464,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>114</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -10466,7 +10474,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -10498,7 +10506,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2736</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -10533,7 +10541,9 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="110"/>
+      <c r="C11" s="110">
+        <v>13</v>
+      </c>
       <c r="D11" s="111"/>
       <c r="E11" s="112"/>
       <c r="F11" s="112"/>
@@ -10541,7 +10551,7 @@
       <c r="H11" s="73"/>
       <c r="I11" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J11" s="77">
         <f t="shared" si="0"/>
@@ -10573,7 +10583,7 @@
       </c>
       <c r="W11" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="X11" s="27"/>
       <c r="AL11" s="12"/>
@@ -10608,7 +10618,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="110">
+        <v>6</v>
+      </c>
       <c r="D12" s="111"/>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
@@ -10616,7 +10628,7 @@
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
@@ -10648,7 +10660,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -10683,47 +10695,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3754</v>
+      </c>
+      <c r="D13" s="114">
+        <v>6</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>45</v>
+      </c>
+      <c r="H13" s="79">
+        <v>24</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3709</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="L13" s="121">
+        <v>17</v>
+      </c>
+      <c r="M13" s="121">
+        <v>18</v>
+      </c>
+      <c r="N13" s="121">
+        <v>18</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="P13" s="121">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>6</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>88998</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -10765,19 +10795,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>4</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -10805,7 +10839,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -10840,7 +10874,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>3</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -10848,7 +10884,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -10880,7 +10916,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -10915,7 +10951,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>2</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -10923,7 +10961,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -10955,7 +10993,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -10990,7 +11028,9 @@
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="110"/>
+      <c r="C17" s="110">
+        <v>1</v>
+      </c>
       <c r="D17" s="111"/>
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
@@ -10998,7 +11038,7 @@
       <c r="H17" s="73"/>
       <c r="I17" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="77">
         <f t="shared" si="4"/>
@@ -11030,7 +11070,7 @@
       </c>
       <c r="W17" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X17" s="27"/>
       <c r="AL17" s="12"/>
@@ -11065,7 +11105,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -11073,7 +11115,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -11105,7 +11147,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -11215,19 +11257,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -11255,7 +11301,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -11290,19 +11336,23 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111">
+        <v>16</v>
+      </c>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
       <c r="G21" s="76"/>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K21" s="41"/>
       <c r="L21" s="112"/>
@@ -11330,7 +11380,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -11365,7 +11415,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>4</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -11373,7 +11425,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -11405,7 +11457,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -11440,19 +11492,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -11480,7 +11536,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -11522,19 +11578,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -11562,7 +11622,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -11604,7 +11664,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>11</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -11612,7 +11674,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -11644,7 +11706,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -11679,19 +11741,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>35</v>
+      </c>
+      <c r="D26" s="111">
+        <v>11</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -11719,7 +11785,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -11735,7 +11801,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>6</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -11743,7 +11811,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="4"/>
@@ -11775,7 +11843,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -11794,7 +11862,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -11802,7 +11872,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="4"/>
@@ -11834,7 +11904,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -11853,15 +11923,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>46</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>4</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
@@ -11872,11 +11946,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>4</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -11885,15 +11961,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -11912,22 +11988,28 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
+      <c r="C30" s="110">
+        <v>68</v>
+      </c>
       <c r="D30" s="111"/>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>2</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K30" s="41"/>
-      <c r="L30" s="112"/>
+      <c r="L30" s="112">
+        <v>2</v>
+      </c>
       <c r="M30" s="112"/>
       <c r="N30" s="112"/>
       <c r="O30" s="112"/>
@@ -11935,7 +12017,7 @@
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="7"/>
@@ -11944,15 +12026,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -11964,22 +12046,28 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>42</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K31" s="41"/>
-      <c r="L31" s="112"/>
+      <c r="L31" s="112">
+        <v>1</v>
+      </c>
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
@@ -11987,7 +12075,7 @@
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="7"/>
@@ -11996,15 +12084,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -12016,7 +12104,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>2</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -12024,7 +12114,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="4"/>
@@ -12056,7 +12146,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -12068,7 +12158,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>5</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -12076,7 +12168,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -12108,7 +12200,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -12120,7 +12212,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>5</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -12128,7 +12222,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="4"/>
@@ -12160,7 +12254,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -12172,30 +12266,40 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>132</v>
+      </c>
+      <c r="D35" s="111">
+        <v>5</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>11</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="112"/>
+      <c r="L35" s="112">
+        <v>10</v>
+      </c>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -12204,15 +12308,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2909</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -12276,7 +12380,9 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>2</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
@@ -12284,7 +12390,7 @@
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="77">
         <f t="shared" si="4"/>
@@ -12316,7 +12422,7 @@
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X37" s="27"/>
     </row>
@@ -12328,30 +12434,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4604</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>398</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4206</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>230</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>60</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>108</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -12360,15 +12478,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>2388</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>25238</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -12380,7 +12498,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>7</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -12388,7 +12508,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="4"/>
@@ -12420,7 +12540,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -12432,7 +12552,9 @@
       <c r="B40" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="116">
+        <v>4</v>
+      </c>
       <c r="D40" s="117"/>
       <c r="E40" s="118"/>
       <c r="F40" s="118"/>
@@ -12440,7 +12562,7 @@
       <c r="H40" s="80"/>
       <c r="I40" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="77">
         <f t="shared" si="4"/>
@@ -12472,7 +12594,7 @@
       </c>
       <c r="W40" s="137">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X40" s="92"/>
     </row>
@@ -12484,7 +12606,9 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
+      <c r="C41" s="146">
+        <v>324</v>
+      </c>
       <c r="D41" s="147"/>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
@@ -12492,7 +12616,7 @@
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
@@ -12524,7 +12648,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7776</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -12536,30 +12660,42 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="164"/>
+      <c r="C42" s="163">
+        <v>1067</v>
+      </c>
+      <c r="D42" s="164">
+        <v>9</v>
+      </c>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>27</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>1</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>7</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>19</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -12568,15 +12704,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>12489</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -12631,30 +12767,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
+      <c r="C44" s="113">
+        <v>34728</v>
+      </c>
       <c r="D44" s="114"/>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>2101</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>32627</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>990</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>570</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>541</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -12663,15 +12809,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>12606</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>195762</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -12727,7 +12873,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>3</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -12735,7 +12883,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="4"/>
@@ -12767,7 +12915,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -12831,19 +12979,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2842</v>
+      </c>
+      <c r="D48" s="142">
+        <v>4</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -12871,7 +13023,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>17056</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -12883,7 +13035,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -12891,7 +13045,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -12923,7 +13077,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -12935,7 +13089,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>10</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -12943,7 +13099,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -12975,7 +13131,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -13039,7 +13195,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -13047,7 +13205,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -13079,7 +13237,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -13091,7 +13249,9 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>2</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
@@ -13099,7 +13259,7 @@
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="77">
         <f t="shared" si="4"/>
@@ -13131,7 +13291,7 @@
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X53" s="27"/>
     </row>
@@ -13143,7 +13303,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>14</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -13151,7 +13313,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -13183,7 +13345,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -13398,11 +13560,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>48109</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -13411,32 +13573,32 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>45520</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>1251</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
@@ -13444,32 +13606,32 @@
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2589</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>16830</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>2589</v>
+      </c>
+      <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>365363</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -13581,10 +13743,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="184" t="s">
+      <c r="C69" s="187" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="185"/>
+      <c r="D69" s="188"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -13907,7 +14069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FEF980-5574-4D62-ABF2-6898880BA2EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F18521-30C6-4E9C-952F-E7D2A7665E71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -13957,7 +14119,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="195">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="Q1" s="196"/>
       <c r="R1" s="196"/>
@@ -14040,7 +14202,7 @@
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="183" t="s">
+      <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="204"/>
@@ -17484,10 +17646,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="181" t="s">
+      <c r="C69" s="184" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="182"/>
+      <c r="D69" s="185"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -17810,7 +17972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E054B12-F159-4771-835F-10B5668BB1C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FEF980-5574-4D62-ABF2-6898880BA2EC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17860,7 +18022,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="195">
-        <v>46116</v>
+        <v>46120</v>
       </c>
       <c r="Q1" s="196"/>
       <c r="R1" s="196"/>
@@ -17943,7 +18105,7 @@
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="189" t="s">
+      <c r="F5" s="183" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="204"/>
@@ -21387,10 +21549,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="187" t="s">
+      <c r="C69" s="181" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="188"/>
+      <c r="D69" s="182"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -21713,7 +21875,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DCBFCF-8FDE-4A25-9852-A6618DD949A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E054B12-F159-4771-835F-10B5668BB1C8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -21763,7 +21925,7 @@
         <v>1</v>
       </c>
       <c r="P1" s="195">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="Q1" s="196"/>
       <c r="R1" s="196"/>

--- a/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
@@ -8,24 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18299A1D-4F90-4F55-A8AB-7E831F1950F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF4AB70-06E2-45BC-949D-88A368BCD50E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
     <sheet name="04,01" sheetId="106" r:id="rId2"/>
     <sheet name="04,06" sheetId="110" r:id="rId3"/>
-    <sheet name="04,07" sheetId="108" r:id="rId4"/>
-    <sheet name="04,08" sheetId="107" r:id="rId5"/>
-    <sheet name="04,09" sheetId="109" r:id="rId6"/>
+    <sheet name="04,08" sheetId="107" r:id="rId4"/>
+    <sheet name="04,09" sheetId="109" r:id="rId5"/>
+    <sheet name="04,10" sheetId="108" r:id="rId6"/>
+    <sheet name="04,11" sheetId="111" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'04,01'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'04,06'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'04,07'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'04,08'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'04,09'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'04,08'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'04,09'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'04,10'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'04,11'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -307,92 +309,6 @@
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{8CC18E23-3D77-4DC5-A5D8-90BF6624E913}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Inventory 
-Bottle Per Case
-All Route</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{83B7FD2E-2D80-4D38-8B0D-3EC8E7DA7464}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Inventory
-Per Case</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{A63857AD-A53C-4E51-A7EC-D51CF6CBEC78}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>User:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Total Ending Inventory
-Bottle Per Case</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>User</author>
-  </authors>
-  <commentList>
     <comment ref="U5" authorId="0" shapeId="0" xr:uid="{C0CCB658-4B40-424D-993B-BA6D18C73D4D}">
       <text>
         <r>
@@ -473,7 +389,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
@@ -559,8 +475,180 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{8CC18E23-3D77-4DC5-A5D8-90BF6624E913}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{83B7FD2E-2D80-4D38-8B0D-3EC8E7DA7464}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{A63857AD-A53C-4E51-A7EC-D51CF6CBEC78}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{3296E700-2895-43F6-A7EC-7FFC6A6438BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{93BC4157-29E2-4BC6-B5AF-FE7050537A68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{23789B3B-32F5-4905-B9F3-CA215E56CADA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2130,7 +2218,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2699,6 +2787,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3138,15 +3235,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="197"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3171,62 +3268,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="201" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203" t="s">
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="207" t="s">
+      <c r="I4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="209" t="s">
+      <c r="L4" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="204"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5477,7 +5574,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="190" t="s">
+      <c r="G62" s="193" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5495,7 +5592,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="191"/>
+      <c r="G63" s="194"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5511,7 +5608,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="192"/>
+      <c r="G64" s="195"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5527,7 +5624,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="193" t="s">
+      <c r="G65" s="196" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5545,7 +5642,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="193"/>
+      <c r="G66" s="196"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5561,7 +5658,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="194"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -5956,17 +6053,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="195">
+      <c r="P1" s="198">
         <v>46113</v>
       </c>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="197"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -5991,62 +6088,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="201" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203" t="s">
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="207" t="s">
+      <c r="I4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="209" t="s">
+      <c r="L4" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="204"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -9574,7 +9671,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="190" t="s">
+      <c r="G62" s="193" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9592,7 +9689,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="191"/>
+      <c r="G63" s="194"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9608,7 +9705,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="192"/>
+      <c r="G64" s="195"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9624,7 +9721,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="193" t="s">
+      <c r="G65" s="196" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9642,7 +9739,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="193"/>
+      <c r="G66" s="196"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9658,7 +9755,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="194"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -10053,17 +10150,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="195">
+      <c r="P1" s="198">
         <v>46118</v>
       </c>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="197"/>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10088,62 +10185,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="201" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203" t="s">
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="207" t="s">
+      <c r="I4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="209" t="s">
+      <c r="L4" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="204"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13639,7 +13736,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="190" t="s">
+      <c r="G62" s="193" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13657,7 +13754,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="191"/>
+      <c r="G63" s="194"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13673,7 +13770,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="192"/>
+      <c r="G64" s="195"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13689,7 +13786,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="193" t="s">
+      <c r="G65" s="196" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13707,7 +13804,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="193"/>
+      <c r="G66" s="196"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13723,7 +13820,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="194"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14069,7 +14166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F18521-30C6-4E9C-952F-E7D2A7665E71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FEF980-5574-4D62-ABF2-6898880BA2EC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -14079,7 +14176,7 @@
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" customWidth="1"/>
@@ -14118,17 +14215,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="195">
-        <v>46119</v>
-      </c>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="197"/>
+      <c r="P1" s="198">
+        <v>46120</v>
+      </c>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14153,62 +14250,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="201" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203" t="s">
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="207" t="s">
+      <c r="I4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="209" t="s">
+      <c r="L4" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="186" t="s">
+      <c r="F5" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="204"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14373,19 +14470,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>53</v>
+      </c>
+      <c r="D8" s="111">
+        <v>21</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -14413,7 +14514,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1293</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -14448,7 +14549,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>104</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -14456,7 +14559,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -14488,7 +14591,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -14523,15 +14626,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>94</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>2</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -14542,11 +14649,13 @@
       <c r="M10" s="112"/>
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
+      <c r="P10" s="112">
+        <v>2</v>
+      </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -14555,15 +14664,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2208</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -14673,7 +14782,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
       <c r="D12" s="111"/>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
@@ -14681,7 +14792,7 @@
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
@@ -14713,7 +14824,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -14748,47 +14859,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3655</v>
+      </c>
+      <c r="D13" s="114">
+        <v>20</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>42</v>
+      </c>
+      <c r="H13" s="79">
+        <v>16</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3613</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
+      <c r="L13" s="121">
+        <v>15</v>
+      </c>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="N13" s="121">
+        <v>7</v>
+      </c>
+      <c r="O13" s="121">
+        <v>4</v>
+      </c>
+      <c r="P13" s="121">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>12</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>86716</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -14830,19 +14959,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>4</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -14870,7 +15003,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -14905,7 +15038,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>3</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -14913,7 +15048,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -14945,7 +15080,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -14980,7 +15115,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>2</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -14988,7 +15125,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -15020,7 +15157,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -15055,7 +15192,9 @@
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="110"/>
+      <c r="C17" s="110">
+        <v>1</v>
+      </c>
       <c r="D17" s="111"/>
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
@@ -15063,7 +15202,7 @@
       <c r="H17" s="73"/>
       <c r="I17" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="77">
         <f t="shared" si="4"/>
@@ -15095,7 +15234,7 @@
       </c>
       <c r="W17" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X17" s="27"/>
       <c r="AL17" s="12"/>
@@ -15130,7 +15269,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -15138,7 +15279,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -15170,7 +15311,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -15280,19 +15421,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -15320,7 +15465,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -15355,19 +15500,23 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111">
+        <v>16</v>
+      </c>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
       <c r="G21" s="76"/>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K21" s="41"/>
       <c r="L21" s="112"/>
@@ -15395,7 +15544,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -15430,7 +15579,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>4</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -15438,7 +15589,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -15470,7 +15621,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -15505,19 +15656,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -15545,7 +15700,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -15587,19 +15742,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -15627,7 +15786,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -15669,7 +15828,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>11</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -15677,7 +15838,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -15709,7 +15870,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -15744,19 +15905,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>35</v>
+      </c>
+      <c r="D26" s="111">
+        <v>11</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -15784,7 +15949,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -15800,7 +15965,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>6</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -15808,7 +15975,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="4"/>
@@ -15840,7 +16007,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -15859,7 +16026,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -15867,7 +16036,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="4"/>
@@ -15899,7 +16068,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -15918,15 +16087,19 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>28</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
+      <c r="G29" s="76">
+        <v>4</v>
+      </c>
       <c r="H29" s="73"/>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
@@ -15937,11 +16110,13 @@
       <c r="M29" s="112"/>
       <c r="N29" s="112"/>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>4</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
@@ -15950,15 +16125,15 @@
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -15977,7 +16152,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
+      <c r="C30" s="110">
+        <v>65</v>
+      </c>
       <c r="D30" s="111"/>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
@@ -15985,7 +16162,7 @@
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
@@ -16017,7 +16194,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -16029,7 +16206,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>40</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -16037,7 +16216,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -16069,7 +16248,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -16081,7 +16260,9 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>1</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
@@ -16089,7 +16270,7 @@
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="77">
         <f t="shared" si="4"/>
@@ -16121,7 +16302,7 @@
       </c>
       <c r="W32" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X32" s="27"/>
     </row>
@@ -16133,7 +16314,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -16141,7 +16324,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -16173,7 +16356,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -16185,7 +16368,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>5</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -16193,7 +16378,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="4"/>
@@ -16225,7 +16410,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -16237,30 +16422,38 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>118</v>
+      </c>
+      <c r="D35" s="111">
+        <v>5</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>2</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>2</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -16269,15 +16462,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2789</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -16341,7 +16534,9 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>2</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
@@ -16349,7 +16544,7 @@
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="77">
         <f t="shared" si="4"/>
@@ -16381,7 +16576,7 @@
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X37" s="27"/>
     </row>
@@ -16393,30 +16588,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>4039</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>142</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3897</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>48</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>94</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -16425,15 +16630,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>23384</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -16445,7 +16650,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>7</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -16453,7 +16660,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="4"/>
@@ -16485,7 +16692,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -16497,7 +16704,9 @@
       <c r="B40" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="116">
+        <v>4</v>
+      </c>
       <c r="D40" s="117"/>
       <c r="E40" s="118"/>
       <c r="F40" s="118"/>
@@ -16505,7 +16714,7 @@
       <c r="H40" s="80"/>
       <c r="I40" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="77">
         <f t="shared" si="4"/>
@@ -16537,7 +16746,7 @@
       </c>
       <c r="W40" s="137">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X40" s="92"/>
     </row>
@@ -16549,7 +16758,9 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
+      <c r="C41" s="146">
+        <v>324</v>
+      </c>
       <c r="D41" s="147"/>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
@@ -16557,7 +16768,7 @@
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
@@ -16589,7 +16800,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7776</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -16601,30 +16812,38 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="164"/>
+      <c r="C42" s="163">
+        <v>1016</v>
+      </c>
+      <c r="D42" s="164">
+        <v>9</v>
+      </c>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>10</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
       <c r="N42" s="165"/>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>10</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -16633,15 +16852,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>12081</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -16696,30 +16915,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
+      <c r="C44" s="113">
+        <v>30849</v>
+      </c>
       <c r="D44" s="114"/>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1467</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>29382</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>540</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>327</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>100</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -16728,15 +16957,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5802</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>176292</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -16792,7 +17021,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>1</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -16800,7 +17031,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="4"/>
@@ -16832,7 +17063,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -16896,19 +17127,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2842</v>
+      </c>
+      <c r="D48" s="142">
+        <v>4</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -16936,7 +17171,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>17056</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -16948,7 +17183,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -16956,7 +17193,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -16988,7 +17225,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -17000,7 +17237,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>4</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -17008,7 +17247,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -17040,7 +17279,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -17104,7 +17343,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -17112,7 +17353,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -17144,7 +17385,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -17156,7 +17397,9 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>2</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
@@ -17164,7 +17407,7 @@
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="77">
         <f t="shared" si="4"/>
@@ -17196,7 +17439,7 @@
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X53" s="27"/>
     </row>
@@ -17208,7 +17451,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>14</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -17216,7 +17461,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -17248,7 +17493,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -17463,11 +17708,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>43432</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -17476,24 +17721,24 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1669</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>41763</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
@@ -17501,40 +17746,40 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1169</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>7974</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>1169</v>
+      </c>
+      <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>339597</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -17542,7 +17787,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="190" t="s">
+      <c r="G62" s="193" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17560,7 +17805,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="191"/>
+      <c r="G63" s="194"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17576,7 +17821,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="192"/>
+      <c r="G64" s="195"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17592,7 +17837,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="193" t="s">
+      <c r="G65" s="196" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17610,7 +17855,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="193"/>
+      <c r="G66" s="196"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17626,7 +17871,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="194"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -17646,10 +17891,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="184" t="s">
+      <c r="C69" s="181" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="185"/>
+      <c r="D69" s="182"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -17972,7 +18217,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FEF980-5574-4D62-ABF2-6898880BA2EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E054B12-F159-4771-835F-10B5668BB1C8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17982,7 +18227,7 @@
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" customWidth="1"/>
@@ -18021,17 +18266,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="195">
-        <v>46120</v>
-      </c>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="197"/>
+      <c r="P1" s="198">
+        <v>46121</v>
+      </c>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18056,62 +18301,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="201" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203" t="s">
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="207" t="s">
+      <c r="I4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="209" t="s">
+      <c r="L4" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="183" t="s">
+      <c r="F5" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="204"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18276,30 +18521,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>53</v>
+      </c>
+      <c r="D8" s="111">
+        <v>21</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
       <c r="M8" s="112"/>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
+      <c r="P8" s="112">
+        <v>1</v>
+      </c>
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -18308,15 +18561,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1269</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -18351,15 +18604,19 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>104</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
-      <c r="G9" s="78"/>
+      <c r="G9" s="78">
+        <v>1</v>
+      </c>
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -18370,11 +18627,13 @@
       <c r="M9" s="121"/>
       <c r="N9" s="121"/>
       <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
+      <c r="P9" s="121">
+        <v>1</v>
+      </c>
       <c r="Q9" s="122"/>
       <c r="R9" s="98">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="125">
         <f t="shared" si="1"/>
@@ -18383,15 +18642,15 @@
       <c r="T9" s="51"/>
       <c r="U9" s="131">
         <f>L9*24+N9*24+P9*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V9" s="132">
         <f>U9/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -18426,7 +18685,9 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>92</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
@@ -18434,7 +18695,7 @@
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -18466,7 +18727,7 @@
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2208</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -18576,7 +18837,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
       <c r="D12" s="111"/>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
@@ -18584,7 +18847,7 @@
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
@@ -18616,7 +18879,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -18651,47 +18914,67 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3613</v>
+      </c>
+      <c r="D13" s="114">
+        <v>4</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>35</v>
+      </c>
+      <c r="H13" s="79">
+        <v>25</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3578</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="L13" s="121">
+        <v>6</v>
+      </c>
+      <c r="M13" s="121">
+        <v>3</v>
+      </c>
+      <c r="N13" s="121">
+        <v>11</v>
+      </c>
+      <c r="O13" s="121">
+        <v>20</v>
+      </c>
+      <c r="P13" s="121">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>2</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>85851</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -18733,19 +19016,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>4</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -18773,7 +19060,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -18808,7 +19095,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>3</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -18816,7 +19105,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -18848,7 +19137,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -18883,7 +19172,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>2</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -18891,7 +19182,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -18923,7 +19214,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -18958,7 +19249,9 @@
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="110"/>
+      <c r="C17" s="110">
+        <v>1</v>
+      </c>
       <c r="D17" s="111"/>
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
@@ -18966,7 +19259,7 @@
       <c r="H17" s="73"/>
       <c r="I17" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="77">
         <f t="shared" si="4"/>
@@ -18998,7 +19291,7 @@
       </c>
       <c r="W17" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X17" s="27"/>
       <c r="AL17" s="12"/>
@@ -19033,7 +19326,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -19041,7 +19336,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -19073,7 +19368,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -19183,19 +19478,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -19223,7 +19522,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -19258,19 +19557,23 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111">
+        <v>16</v>
+      </c>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
       <c r="G21" s="76"/>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K21" s="41"/>
       <c r="L21" s="112"/>
@@ -19298,7 +19601,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -19333,7 +19636,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>4</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -19341,7 +19646,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -19373,7 +19678,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -19408,19 +19713,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -19448,7 +19757,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -19490,19 +19799,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -19530,7 +19843,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -19572,7 +19885,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>11</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -19580,7 +19895,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -19612,7 +19927,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -19647,30 +19962,38 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>35</v>
+      </c>
+      <c r="D26" s="111">
+        <v>11</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
-      <c r="G26" s="76"/>
+      <c r="G26" s="76">
+        <v>1</v>
+      </c>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
       <c r="M26" s="112"/>
       <c r="N26" s="112"/>
       <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
+      <c r="P26" s="112">
+        <v>1</v>
+      </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="124">
         <f t="shared" si="7"/>
@@ -19679,15 +20002,15 @@
       <c r="T26" s="41"/>
       <c r="U26" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V26" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -19703,7 +20026,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>6</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -19711,7 +20036,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="4"/>
@@ -19743,7 +20068,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -19762,7 +20087,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -19770,7 +20097,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="4"/>
@@ -19802,7 +20129,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -19821,47 +20148,61 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="110"/>
+      <c r="C29" s="110">
+        <v>24</v>
+      </c>
       <c r="D29" s="111"/>
       <c r="E29" s="112"/>
       <c r="F29" s="112"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="76">
+        <v>5</v>
+      </c>
+      <c r="H29" s="73">
+        <v>12</v>
+      </c>
       <c r="I29" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J29" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="K29" s="42"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
+      <c r="L29" s="112">
+        <v>1</v>
+      </c>
+      <c r="M29" s="112">
+        <v>12</v>
+      </c>
+      <c r="N29" s="112">
+        <v>1</v>
+      </c>
       <c r="O29" s="112"/>
-      <c r="P29" s="112"/>
+      <c r="P29" s="112">
+        <v>3</v>
+      </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S29" s="124">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T29" s="42"/>
       <c r="U29" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V29" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W29" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="X29" s="27"/>
       <c r="Y29" s="2"/>
@@ -19880,7 +20221,9 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
+      <c r="C30" s="110">
+        <v>65</v>
+      </c>
       <c r="D30" s="111"/>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
@@ -19888,7 +20231,7 @@
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
@@ -19920,7 +20263,7 @@
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -19932,7 +20275,9 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>40</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
@@ -19940,7 +20285,7 @@
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -19972,7 +20317,7 @@
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -19984,11 +20329,15 @@
       <c r="B32" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="110">
+        <v>1</v>
+      </c>
       <c r="D32" s="111"/>
       <c r="E32" s="112"/>
       <c r="F32" s="112"/>
-      <c r="G32" s="76"/>
+      <c r="G32" s="76">
+        <v>1</v>
+      </c>
       <c r="H32" s="73"/>
       <c r="I32" s="73">
         <f t="shared" si="4"/>
@@ -20003,11 +20352,13 @@
       <c r="M32" s="112"/>
       <c r="N32" s="112"/>
       <c r="O32" s="112"/>
-      <c r="P32" s="112"/>
+      <c r="P32" s="112">
+        <v>1</v>
+      </c>
       <c r="Q32" s="120"/>
       <c r="R32" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="124">
         <f t="shared" si="7"/>
@@ -20016,11 +20367,11 @@
       <c r="T32" s="41"/>
       <c r="U32" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V32" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="129">
         <f t="shared" si="8"/>
@@ -20036,7 +20387,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>4</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -20044,7 +20397,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -20076,7 +20429,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -20088,7 +20441,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>5</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -20096,7 +20451,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="4"/>
@@ -20128,7 +20483,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -20140,19 +20495,23 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>116</v>
+      </c>
+      <c r="D35" s="111">
+        <v>5</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
       <c r="G35" s="76"/>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
@@ -20180,7 +20539,7 @@
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2789</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -20244,7 +20603,9 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>2</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
@@ -20252,7 +20613,7 @@
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="77">
         <f t="shared" si="4"/>
@@ -20284,7 +20645,7 @@
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X37" s="27"/>
     </row>
@@ -20296,30 +20657,42 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3897</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>51</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3846</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="51"/>
-      <c r="L38" s="121"/>
+      <c r="L38" s="121">
+        <v>20</v>
+      </c>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>12</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>19</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -20328,15 +20701,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>23078</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -20348,7 +20721,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>7</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -20356,7 +20731,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="4"/>
@@ -20388,7 +20763,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -20400,7 +20775,9 @@
       <c r="B40" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="116">
+        <v>4</v>
+      </c>
       <c r="D40" s="117"/>
       <c r="E40" s="118"/>
       <c r="F40" s="118"/>
@@ -20408,7 +20785,7 @@
       <c r="H40" s="80"/>
       <c r="I40" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="77">
         <f t="shared" si="4"/>
@@ -20440,7 +20817,7 @@
       </c>
       <c r="W40" s="137">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X40" s="92"/>
     </row>
@@ -20452,7 +20829,9 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
+      <c r="C41" s="146">
+        <v>324</v>
+      </c>
       <c r="D41" s="147"/>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
@@ -20460,7 +20839,7 @@
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
@@ -20492,7 +20871,7 @@
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>7776</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -20504,30 +20883,42 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="164"/>
+      <c r="C42" s="163">
+        <v>1006</v>
+      </c>
+      <c r="D42" s="164">
+        <v>9</v>
+      </c>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>37</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K42" s="169"/>
-      <c r="L42" s="165"/>
+      <c r="L42" s="165">
+        <v>2</v>
+      </c>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>3</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>32</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -20536,15 +20927,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>11637</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -20599,30 +20990,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
+      <c r="C44" s="113">
+        <v>29382</v>
+      </c>
       <c r="D44" s="114"/>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>1375</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>28007</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K44" s="51"/>
-      <c r="L44" s="121"/>
+      <c r="L44" s="121">
+        <v>535</v>
+      </c>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>317</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>523</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -20631,15 +21032,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>8250</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>168042</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -20695,7 +21096,9 @@
       <c r="B46" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="110"/>
+      <c r="C46" s="110">
+        <v>1</v>
+      </c>
       <c r="D46" s="111"/>
       <c r="E46" s="112"/>
       <c r="F46" s="112"/>
@@ -20703,7 +21106,7 @@
       <c r="H46" s="73"/>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="77">
         <f t="shared" si="4"/>
@@ -20735,7 +21138,7 @@
       </c>
       <c r="W46" s="129">
         <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X46" s="27"/>
     </row>
@@ -20799,19 +21202,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2842</v>
+      </c>
+      <c r="D48" s="142">
+        <v>4</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -20839,7 +21246,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>17056</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -20851,7 +21258,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -20859,7 +21268,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -20891,7 +21300,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -20903,7 +21312,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>4</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -20911,7 +21322,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -20943,7 +21354,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -21007,7 +21418,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -21015,7 +21428,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -21047,7 +21460,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -21059,7 +21472,9 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>2</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
@@ -21067,7 +21482,7 @@
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="77">
         <f t="shared" si="4"/>
@@ -21099,7 +21514,7 @@
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X53" s="27"/>
     </row>
@@ -21111,7 +21526,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>14</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -21119,7 +21536,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -21151,7 +21568,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -21366,11 +21783,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>41763</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -21379,65 +21796,65 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>1507</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>40256</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
         <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="M60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1507</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>10056</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>1507</v>
+      </c>
+      <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>329504</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -21445,7 +21862,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="190" t="s">
+      <c r="G62" s="193" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21463,7 +21880,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="191"/>
+      <c r="G63" s="194"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21479,7 +21896,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="192"/>
+      <c r="G64" s="195"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -21495,7 +21912,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="193" t="s">
+      <c r="G65" s="196" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -21513,7 +21930,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="193"/>
+      <c r="G66" s="196"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -21529,7 +21946,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="194"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -21549,10 +21966,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="181" t="s">
+      <c r="C69" s="187" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="182"/>
+      <c r="D69" s="188"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -21875,7 +22292,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E054B12-F159-4771-835F-10B5668BB1C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F18521-30C6-4E9C-952F-E7D2A7665E71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -21924,17 +22341,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="195">
-        <v>46121</v>
-      </c>
-      <c r="Q1" s="196"/>
-      <c r="R1" s="196"/>
-      <c r="S1" s="196"/>
-      <c r="T1" s="196"/>
-      <c r="U1" s="196"/>
-      <c r="V1" s="196"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="197"/>
+      <c r="P1" s="198">
+        <v>46122</v>
+      </c>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -21959,62 +22376,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="201" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="200" t="s">
+      <c r="D4" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="201" t="s">
+      <c r="E4" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203" t="s">
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="205" t="s">
+      <c r="H4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="207" t="s">
+      <c r="I4" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="205" t="s">
+      <c r="J4" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="209" t="s">
+      <c r="L4" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="199"/>
-      <c r="D5" s="200"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="189" t="s">
+      <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="204"/>
-      <c r="H5" s="206"/>
-      <c r="I5" s="208"/>
-      <c r="J5" s="206"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25348,7 +25765,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="190" t="s">
+      <c r="G62" s="193" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -25366,7 +25783,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="191"/>
+      <c r="G63" s="194"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -25382,7 +25799,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="192"/>
+      <c r="G64" s="195"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -25398,7 +25815,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="193" t="s">
+      <c r="G65" s="196" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -25416,7 +25833,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="193"/>
+      <c r="G66" s="196"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -25432,7 +25849,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="194"/>
+      <c r="G67" s="197"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -25452,10 +25869,3913 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="187" t="s">
+      <c r="C69" s="184" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="188"/>
+      <c r="D69" s="185"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB432E16-B4D4-47C5-ADDB-2F0F21F00F0F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="198">
+        <v>46123</v>
+      </c>
+      <c r="Q1" s="199"/>
+      <c r="R1" s="199"/>
+      <c r="S1" s="199"/>
+      <c r="T1" s="199"/>
+      <c r="U1" s="199"/>
+      <c r="V1" s="199"/>
+      <c r="W1" s="199"/>
+      <c r="X1" s="200"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="201" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="202" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="203" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="204" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="205"/>
+      <c r="G4" s="206" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="208" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="210" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="208" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="212" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="214"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="215"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="203"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="207"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="209"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="110"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112"/>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112"/>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110"/>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112"/>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110"/>
+      <c r="D35" s="111"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113"/>
+      <c r="D38" s="114"/>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>0</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>0</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110"/>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>0</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165"/>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165"/>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>0</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>0</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113"/>
+      <c r="D44" s="114"/>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121"/>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>0</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>0</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>0</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110"/>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>0</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110"/>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141"/>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>0</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>0</v>
+      </c>
+      <c r="W60" s="90">
+        <f>SUM(W8:W59)</f>
+        <v>0</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="193" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="194"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="195"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="196" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="196"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="197"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="190" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="191"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>

--- a/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/DSSR GBDS MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5335A894-2025-4DA8-95C6-AA2932051952}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAF8ED5-D9E1-4EC3-BCD2-A081765691F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE" sheetId="89" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="04,15" sheetId="111" r:id="rId7"/>
     <sheet name="04,16" sheetId="112" r:id="rId8"/>
     <sheet name="04,17" sheetId="113" r:id="rId9"/>
-    <sheet name="04,18" sheetId="114" r:id="rId10"/>
+    <sheet name="04,20" sheetId="114" r:id="rId10"/>
+    <sheet name="04,21" sheetId="115" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'04,01'!$A$1:$Y$61</definedName>
@@ -33,7 +34,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'04,15'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'04,16'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'04,17'!$A$1:$Y$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'04,18'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'04,20'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'04,21'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">EXAMPLE!$A$1:$Y$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -195,6 +197,92 @@
       </text>
     </comment>
     <comment ref="W5" authorId="0" shapeId="0" xr:uid="{8554FF69-0758-4A33-8E53-F7B7EB41DD68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{B69EC2D9-C41E-44A6-AD04-D92001559F5D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{44593FE7-658D-47BC-8919-6739FDB2702F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{0E001D5D-F15A-495C-9CA5-42A5AACEC989}">
       <text>
         <r>
           <rPr>
@@ -912,7 +1000,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="82">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -2482,7 +2570,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3069,6 +3157,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3508,15 +3605,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="P1" s="204"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -3541,62 +3638,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -5847,7 +5944,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -5865,7 +5962,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -5881,7 +5978,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -5897,7 +5994,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -5915,7 +6012,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -5931,7 +6028,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -6287,7 +6384,7 @@
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" customWidth="1"/>
@@ -6326,17 +6423,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
-        <v>46130</v>
-      </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="P1" s="204">
+        <v>46132</v>
+      </c>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -6361,62 +6458,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="195" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -6581,19 +6678,23 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>41</v>
+      </c>
+      <c r="D8" s="111">
+        <v>19</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
       <c r="G8" s="76"/>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
@@ -6621,7 +6722,7 @@
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -6656,7 +6757,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>101</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -6664,7 +6767,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -6696,7 +6799,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2424</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -6731,30 +6834,40 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>70</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>14</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="41"/>
-      <c r="L10" s="112"/>
+      <c r="L10" s="112">
+        <v>2</v>
+      </c>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>2</v>
+      </c>
       <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
+      <c r="P10" s="112">
+        <v>10</v>
+      </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -6763,15 +6876,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -6881,7 +6994,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="110">
+        <v>4</v>
+      </c>
       <c r="D12" s="111"/>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
@@ -6889,7 +7004,7 @@
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
@@ -6921,7 +7036,7 @@
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -6956,47 +7071,65 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3395</v>
+      </c>
+      <c r="D13" s="114">
+        <v>21</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>40</v>
+      </c>
+      <c r="H13" s="79">
+        <v>22</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3355</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
+      <c r="L13" s="121">
+        <v>6</v>
+      </c>
+      <c r="M13" s="121">
+        <v>20</v>
+      </c>
+      <c r="N13" s="121">
+        <v>16</v>
+      </c>
       <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="P13" s="121">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>2</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>80519</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -7038,19 +7171,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>4</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -7078,7 +7215,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -7113,7 +7250,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>3</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -7121,7 +7260,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -7153,7 +7292,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -7188,7 +7327,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>2</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -7196,7 +7337,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -7228,7 +7369,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -7263,7 +7404,9 @@
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="110"/>
+      <c r="C17" s="110">
+        <v>1</v>
+      </c>
       <c r="D17" s="111"/>
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
@@ -7271,7 +7414,7 @@
       <c r="H17" s="73"/>
       <c r="I17" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="77">
         <f t="shared" si="4"/>
@@ -7303,7 +7446,7 @@
       </c>
       <c r="W17" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X17" s="27"/>
       <c r="AL17" s="12"/>
@@ -7338,7 +7481,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -7346,7 +7491,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -7378,7 +7523,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -7488,19 +7633,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -7528,7 +7677,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -7563,19 +7712,23 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111">
+        <v>16</v>
+      </c>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
       <c r="G21" s="76"/>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K21" s="41"/>
       <c r="L21" s="112"/>
@@ -7603,7 +7756,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -7638,7 +7791,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>4</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -7646,7 +7801,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -7678,7 +7833,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -7713,19 +7868,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -7753,7 +7912,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -7795,19 +7954,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -7835,7 +7998,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -7877,7 +8040,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>11</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -7885,7 +8050,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -7917,7 +8082,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -7952,6 +8117,4011 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="C26" s="110">
+        <v>3</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="76">
+        <v>3</v>
+      </c>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="112">
+        <v>1</v>
+      </c>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="120"/>
+      <c r="R26" s="86">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="S26" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="41"/>
+      <c r="U26" s="107">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="V26" s="130">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="W26" s="129">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="X26" s="27"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="110">
+        <v>6</v>
+      </c>
+      <c r="D27" s="111"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J27" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="42"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="112"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="120"/>
+      <c r="R27" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="42"/>
+      <c r="U27" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="129">
+        <f t="shared" si="8"/>
+        <v>144</v>
+      </c>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J28" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="42"/>
+      <c r="L28" s="112"/>
+      <c r="M28" s="112"/>
+      <c r="N28" s="112"/>
+      <c r="O28" s="112"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="42"/>
+      <c r="U28" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="129">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="110"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="112"/>
+      <c r="F29" s="112"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="42"/>
+      <c r="L29" s="112"/>
+      <c r="M29" s="112"/>
+      <c r="N29" s="112"/>
+      <c r="O29" s="112"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="42"/>
+      <c r="U29" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W29" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="110">
+        <v>57</v>
+      </c>
+      <c r="D30" s="111"/>
+      <c r="E30" s="112"/>
+      <c r="F30" s="112"/>
+      <c r="G30" s="76">
+        <v>4</v>
+      </c>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73">
+        <f t="shared" si="4"/>
+        <v>53</v>
+      </c>
+      <c r="J30" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="112">
+        <v>3</v>
+      </c>
+      <c r="M30" s="112"/>
+      <c r="N30" s="112">
+        <v>1</v>
+      </c>
+      <c r="O30" s="112"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="86">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="S30" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="41"/>
+      <c r="U30" s="107">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="V30" s="130">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="W30" s="129">
+        <f t="shared" si="8"/>
+        <v>1272</v>
+      </c>
+      <c r="X30" s="27"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="110">
+        <v>34</v>
+      </c>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="J31" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="41"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112">
+        <v>1</v>
+      </c>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="124">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="T31" s="41"/>
+      <c r="U31" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="129">
+        <f t="shared" si="8"/>
+        <v>792</v>
+      </c>
+      <c r="X31" s="27"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="110"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="41"/>
+      <c r="L32" s="112"/>
+      <c r="M32" s="112"/>
+      <c r="N32" s="112"/>
+      <c r="O32" s="112"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="120"/>
+      <c r="R32" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="41"/>
+      <c r="U32" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="27"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="110">
+        <v>2</v>
+      </c>
+      <c r="D33" s="111"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="76">
+        <v>1</v>
+      </c>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="41"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112">
+        <v>1</v>
+      </c>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="120"/>
+      <c r="R33" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S33" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="41"/>
+      <c r="U33" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V33" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W33" s="129">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="X33" s="27"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="110">
+        <v>4</v>
+      </c>
+      <c r="D34" s="111"/>
+      <c r="E34" s="112"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="76">
+        <v>1</v>
+      </c>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J34" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="41"/>
+      <c r="L34" s="112"/>
+      <c r="M34" s="112"/>
+      <c r="N34" s="112">
+        <v>1</v>
+      </c>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="120"/>
+      <c r="R34" s="86">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="S34" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="41"/>
+      <c r="U34" s="107">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="V34" s="130">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W34" s="129">
+        <f t="shared" si="8"/>
+        <v>72</v>
+      </c>
+      <c r="X34" s="27"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="110">
+        <v>94</v>
+      </c>
+      <c r="D35" s="111">
+        <v>1</v>
+      </c>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73">
+        <f t="shared" si="4"/>
+        <v>94</v>
+      </c>
+      <c r="J35" s="77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K35" s="41"/>
+      <c r="L35" s="112"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="120"/>
+      <c r="R35" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="41"/>
+      <c r="U35" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="129">
+        <f t="shared" si="8"/>
+        <v>2257</v>
+      </c>
+      <c r="X35" s="27"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="110"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="112"/>
+      <c r="F36" s="112"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="112"/>
+      <c r="M36" s="112"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="112"/>
+      <c r="P36" s="112"/>
+      <c r="Q36" s="120"/>
+      <c r="R36" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="41"/>
+      <c r="U36" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="27"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="110">
+        <v>2</v>
+      </c>
+      <c r="D37" s="111"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J37" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="41"/>
+      <c r="L37" s="112"/>
+      <c r="M37" s="112"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="112"/>
+      <c r="P37" s="112"/>
+      <c r="Q37" s="120"/>
+      <c r="R37" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="41"/>
+      <c r="U37" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="129">
+        <f t="shared" si="8"/>
+        <v>48</v>
+      </c>
+      <c r="X37" s="27"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="113">
+        <v>3239</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="78">
+        <v>346</v>
+      </c>
+      <c r="H38" s="79"/>
+      <c r="I38" s="139">
+        <f t="shared" si="4"/>
+        <v>2893</v>
+      </c>
+      <c r="J38" s="140">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="51"/>
+      <c r="L38" s="121">
+        <v>123</v>
+      </c>
+      <c r="M38" s="121"/>
+      <c r="N38" s="121">
+        <v>129</v>
+      </c>
+      <c r="O38" s="121"/>
+      <c r="P38" s="121">
+        <v>94</v>
+      </c>
+      <c r="Q38" s="122"/>
+      <c r="R38" s="97">
+        <f t="shared" si="7"/>
+        <v>346</v>
+      </c>
+      <c r="S38" s="125">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="51"/>
+      <c r="U38" s="131">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>2076</v>
+      </c>
+      <c r="V38" s="135">
+        <f>U38/6</f>
+        <v>346</v>
+      </c>
+      <c r="W38" s="133">
+        <f>I38*6+J38</f>
+        <v>17360</v>
+      </c>
+      <c r="X38" s="52"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="110">
+        <v>7</v>
+      </c>
+      <c r="D39" s="111"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="76">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="J39" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="112"/>
+      <c r="M39" s="112"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="112"/>
+      <c r="P39" s="112"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="41"/>
+      <c r="U39" s="107">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="129">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>168</v>
+      </c>
+      <c r="X39" s="27"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="116">
+        <v>4</v>
+      </c>
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J40" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="41"/>
+      <c r="L40" s="112"/>
+      <c r="M40" s="112"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="112"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="120"/>
+      <c r="R40" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="41"/>
+      <c r="U40" s="136">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="137">
+        <f t="shared" si="10"/>
+        <v>96</v>
+      </c>
+      <c r="X40" s="92"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="146">
+        <v>251</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="151">
+        <f t="shared" si="4"/>
+        <v>251</v>
+      </c>
+      <c r="J41" s="152">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K41" s="153"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="154"/>
+      <c r="N41" s="154"/>
+      <c r="O41" s="154"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="155"/>
+      <c r="R41" s="156">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="157">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="153"/>
+      <c r="U41" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="159">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="159">
+        <f t="shared" si="10"/>
+        <v>6044</v>
+      </c>
+      <c r="X41" s="160"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="163">
+        <v>806</v>
+      </c>
+      <c r="D42" s="164"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="166">
+        <v>28</v>
+      </c>
+      <c r="H42" s="167"/>
+      <c r="I42" s="166">
+        <f t="shared" si="4"/>
+        <v>778</v>
+      </c>
+      <c r="J42" s="168">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="169"/>
+      <c r="L42" s="165">
+        <v>8</v>
+      </c>
+      <c r="M42" s="165"/>
+      <c r="N42" s="165">
+        <v>5</v>
+      </c>
+      <c r="O42" s="165"/>
+      <c r="P42" s="165">
+        <v>15</v>
+      </c>
+      <c r="Q42" s="170"/>
+      <c r="R42" s="171">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="S42" s="172">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="169"/>
+      <c r="U42" s="173">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>336</v>
+      </c>
+      <c r="V42" s="174">
+        <f>U42/12</f>
+        <v>28</v>
+      </c>
+      <c r="W42" s="175">
+        <f>I42*12+J42</f>
+        <v>9336</v>
+      </c>
+      <c r="X42" s="176"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="110"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="112"/>
+      <c r="F43" s="112"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="94">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="41"/>
+      <c r="L43" s="112"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="112"/>
+      <c r="P43" s="112"/>
+      <c r="Q43" s="120"/>
+      <c r="R43" s="161">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="41"/>
+      <c r="U43" s="107"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="129"/>
+      <c r="X43" s="27"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="113">
+        <v>21921</v>
+      </c>
+      <c r="D44" s="114">
+        <v>3</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="115"/>
+      <c r="G44" s="78">
+        <v>1344</v>
+      </c>
+      <c r="H44" s="79"/>
+      <c r="I44" s="73">
+        <f>C44+E44-G44</f>
+        <v>20577</v>
+      </c>
+      <c r="J44" s="177">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="K44" s="51"/>
+      <c r="L44" s="121">
+        <v>582</v>
+      </c>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121">
+        <v>368</v>
+      </c>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121">
+        <v>394</v>
+      </c>
+      <c r="Q44" s="122"/>
+      <c r="R44" s="178">
+        <f t="shared" si="7"/>
+        <v>1344</v>
+      </c>
+      <c r="S44" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="51"/>
+      <c r="U44" s="131">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>8064</v>
+      </c>
+      <c r="V44" s="130">
+        <f>U44/6</f>
+        <v>1344</v>
+      </c>
+      <c r="W44" s="133">
+        <f>I44*6+J44</f>
+        <v>123465</v>
+      </c>
+      <c r="X44" s="52"/>
+      <c r="Z44" s="47"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="110"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="112"/>
+      <c r="M45" s="112"/>
+      <c r="N45" s="112"/>
+      <c r="O45" s="112"/>
+      <c r="P45" s="112"/>
+      <c r="Q45" s="120"/>
+      <c r="R45" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="107"/>
+      <c r="V45" s="132"/>
+      <c r="W45" s="129"/>
+      <c r="X45" s="27"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="110"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="41"/>
+      <c r="L46" s="112"/>
+      <c r="M46" s="112"/>
+      <c r="N46" s="112"/>
+      <c r="O46" s="112"/>
+      <c r="P46" s="112"/>
+      <c r="Q46" s="120"/>
+      <c r="R46" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="128">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="107">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="134">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="129">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="27"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="110"/>
+      <c r="D47" s="111"/>
+      <c r="E47" s="112"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="41"/>
+      <c r="L47" s="112"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="112"/>
+      <c r="O47" s="112"/>
+      <c r="P47" s="112"/>
+      <c r="Q47" s="120"/>
+      <c r="R47" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="107">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="130">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="129">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="27"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="141">
+        <v>2830</v>
+      </c>
+      <c r="D48" s="142">
+        <v>4</v>
+      </c>
+      <c r="E48" s="121"/>
+      <c r="F48" s="121"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="139">
+        <f t="shared" si="4"/>
+        <v>2830</v>
+      </c>
+      <c r="J48" s="140">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K48" s="51"/>
+      <c r="L48" s="121"/>
+      <c r="M48" s="121"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="122"/>
+      <c r="R48" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="51"/>
+      <c r="U48" s="131">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="135">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="133">
+        <f>I48*6+J48</f>
+        <v>16984</v>
+      </c>
+      <c r="X48" s="52"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
+      <c r="D49" s="111"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J49" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="41"/>
+      <c r="L49" s="112"/>
+      <c r="M49" s="112"/>
+      <c r="N49" s="112"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="120"/>
+      <c r="R49" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="41"/>
+      <c r="U49" s="107">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="109">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="129">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>24</v>
+      </c>
+      <c r="X49" s="27"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="110">
+        <v>4</v>
+      </c>
+      <c r="D50" s="111"/>
+      <c r="E50" s="112"/>
+      <c r="F50" s="112"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J50" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="41"/>
+      <c r="L50" s="112"/>
+      <c r="M50" s="112"/>
+      <c r="N50" s="112"/>
+      <c r="O50" s="112"/>
+      <c r="P50" s="112"/>
+      <c r="Q50" s="120"/>
+      <c r="R50" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="41"/>
+      <c r="U50" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="129">
+        <f t="shared" si="16"/>
+        <v>96</v>
+      </c>
+      <c r="X50" s="27"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="110"/>
+      <c r="D51" s="111"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="41"/>
+      <c r="L51" s="112"/>
+      <c r="M51" s="112"/>
+      <c r="N51" s="112"/>
+      <c r="O51" s="112"/>
+      <c r="P51" s="112"/>
+      <c r="Q51" s="120"/>
+      <c r="R51" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="41"/>
+      <c r="U51" s="107">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="130">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="129">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="27"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
+      <c r="D52" s="142"/>
+      <c r="E52" s="121"/>
+      <c r="F52" s="121"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="139"/>
+      <c r="I52" s="139">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="140">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="51"/>
+      <c r="L52" s="121"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="144">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="51"/>
+      <c r="U52" s="131">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="135">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="133">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="52"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="110">
+        <v>2</v>
+      </c>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="112"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J53" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="41"/>
+      <c r="L53" s="112"/>
+      <c r="M53" s="112"/>
+      <c r="N53" s="112"/>
+      <c r="O53" s="112"/>
+      <c r="P53" s="112"/>
+      <c r="Q53" s="120"/>
+      <c r="R53" s="96">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="41"/>
+      <c r="U53" s="107">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="109">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="129">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>48</v>
+      </c>
+      <c r="X53" s="27"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="110">
+        <v>14</v>
+      </c>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="112"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="J54" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="41"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="41"/>
+      <c r="U54" s="107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="130">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="129">
+        <f t="shared" si="19"/>
+        <v>336</v>
+      </c>
+      <c r="X54" s="27"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="110"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="41"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="41"/>
+      <c r="U55" s="107"/>
+      <c r="V55" s="130"/>
+      <c r="W55" s="129"/>
+      <c r="X55" s="27"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="110"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="41"/>
+      <c r="L56" s="112"/>
+      <c r="M56" s="112"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="112"/>
+      <c r="P56" s="112"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="41"/>
+      <c r="U56" s="107"/>
+      <c r="V56" s="130"/>
+      <c r="W56" s="129"/>
+      <c r="X56" s="27"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="110"/>
+      <c r="D57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="112"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="41"/>
+      <c r="L57" s="112"/>
+      <c r="M57" s="112"/>
+      <c r="N57" s="112"/>
+      <c r="O57" s="112"/>
+      <c r="P57" s="112"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="107"/>
+      <c r="V57" s="130"/>
+      <c r="W57" s="129"/>
+      <c r="X57" s="27"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="110"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="41"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="120"/>
+      <c r="R58" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="41"/>
+      <c r="U58" s="107"/>
+      <c r="V58" s="130"/>
+      <c r="W58" s="129"/>
+      <c r="X58" s="27"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="110"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="41"/>
+      <c r="L59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="41"/>
+      <c r="U59" s="107"/>
+      <c r="V59" s="130"/>
+      <c r="W59" s="129"/>
+      <c r="X59" s="27"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="43">
+        <f>SUM(C8:C59)</f>
+        <v>33006</v>
+      </c>
+      <c r="D60" s="54">
+        <f>SUM(D8:D59)</f>
+        <v>162</v>
+      </c>
+      <c r="E60" s="44">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="28">
+        <f>SUM(G8:G59)</f>
+        <v>1782</v>
+      </c>
+      <c r="H60" s="56">
+        <f>SUM(H8:H59)</f>
+        <v>22</v>
+      </c>
+      <c r="I60" s="56">
+        <f>SUM(I8:I59)</f>
+        <v>31224</v>
+      </c>
+      <c r="J60" s="45">
+        <f>SUM(J8:J59)</f>
+        <v>140</v>
+      </c>
+      <c r="K60" s="46"/>
+      <c r="L60" s="74">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>725</v>
+      </c>
+      <c r="M60" s="74">
+        <f t="shared" si="20"/>
+        <v>21</v>
+      </c>
+      <c r="N60" s="74">
+        <f t="shared" si="20"/>
+        <v>523</v>
+      </c>
+      <c r="O60" s="74">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="74">
+        <f t="shared" si="20"/>
+        <v>533</v>
+      </c>
+      <c r="Q60" s="75">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="R60" s="85">
+        <f t="shared" si="20"/>
+        <v>1781</v>
+      </c>
+      <c r="S60" s="84">
+        <f t="shared" si="20"/>
+        <v>23</v>
+      </c>
+      <c r="T60" s="46"/>
+      <c r="U60" s="43">
+        <f>SUM(U8:U59)</f>
+        <v>11988</v>
+      </c>
+      <c r="V60" s="102">
+        <f>SUM(V8:V59)</f>
+        <v>1781</v>
+      </c>
+      <c r="W60" s="180">
+        <f>SUM(W8:W59)</f>
+        <v>266168</v>
+      </c>
+      <c r="X60" s="45"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="103"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="199" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="30"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="67"/>
+      <c r="R62" s="67"/>
+      <c r="S62" s="32"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="200"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="63"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="68"/>
+      <c r="R63" s="68"/>
+      <c r="S63" s="35"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="201"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="36"/>
+      <c r="M64" s="64"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="37"/>
+      <c r="Q64" s="69"/>
+      <c r="R64" s="69"/>
+      <c r="S64" s="38"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="202" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="64"/>
+      <c r="N65" s="37"/>
+      <c r="O65" s="37"/>
+      <c r="P65" s="37"/>
+      <c r="Q65" s="69"/>
+      <c r="R65" s="69"/>
+      <c r="S65" s="38"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="202"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="33"/>
+      <c r="M66" s="63"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="68"/>
+      <c r="R66" s="68"/>
+      <c r="S66" s="35"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="203"/>
+      <c r="H67" s="61"/>
+      <c r="I67" s="61"/>
+      <c r="J67" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="39"/>
+      <c r="M67" s="65"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="70"/>
+      <c r="R67" s="70"/>
+      <c r="S67" s="29"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="193" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="194"/>
+      <c r="E69" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="66"/>
+      <c r="N69" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="71"/>
+      <c r="R69" s="71"/>
+      <c r="S69" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="22"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="22"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="X71" s="22"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="X72" s="22"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="X74" s="22"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="X75" s="22"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="X76" s="22"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="X78" s="22"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="X79" s="22"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="22"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="X80" s="22"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="22"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="X82" s="22"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="22"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="X83" s="22"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="X84" s="22"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="X86" s="22"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="X87" s="22"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="X88" s="22"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="X90" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6456E53-6248-4078-915F-672ED3CC18D9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="204">
+        <v>46133</v>
+      </c>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="49"/>
+      <c r="B4" s="207" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="208" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="209" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="210" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="214" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="216" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="214" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="218" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="198" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="119"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="41"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="109"/>
+      <c r="W6" s="129"/>
+      <c r="X6" s="27"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="27"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="77">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="86">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="41"/>
+      <c r="U8" s="107">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="130">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="129">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="27"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="113"/>
+      <c r="D9" s="114"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="78">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="51"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="131">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="132">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="52"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="110"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="41"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="41"/>
+      <c r="U10" s="107">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="134">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="27"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="112"/>
+      <c r="P11" s="112"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="41"/>
+      <c r="U11" s="107">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="130">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="27"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="77">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="41"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="41"/>
+      <c r="U12" s="107">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="130">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="129">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="27"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="113"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="80">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="94">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="53"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="97">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="125">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="53"/>
+      <c r="U13" s="131">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="135">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="133">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="95">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="41"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="96">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="126">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="41"/>
+      <c r="U14" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="109">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="129">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="27"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="41"/>
+      <c r="U15" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="27"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="27"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="112"/>
+      <c r="M17" s="112"/>
+      <c r="N17" s="112"/>
+      <c r="O17" s="112"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="27"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="41"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="41"/>
+      <c r="U18" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="27"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="41"/>
+      <c r="U19" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="27"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="41"/>
+      <c r="L20" s="112"/>
+      <c r="M20" s="112"/>
+      <c r="N20" s="112"/>
+      <c r="O20" s="112"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="41"/>
+      <c r="U20" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="27"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="41"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="41"/>
+      <c r="U21" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="27"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="112"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="112"/>
+      <c r="M22" s="112"/>
+      <c r="N22" s="112"/>
+      <c r="O22" s="112"/>
+      <c r="P22" s="112"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="41"/>
+      <c r="U22" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="27"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="42"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="42"/>
+      <c r="U23" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="27"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="110"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="42"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="120"/>
+      <c r="R24" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="42"/>
+      <c r="U24" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="77">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="112"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="120"/>
+      <c r="R25" s="86">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="124">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="41"/>
+      <c r="U25" s="107">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="130">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="129">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="27"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
       <c r="C26" s="110"/>
       <c r="D26" s="111"/>
       <c r="E26" s="112"/>
@@ -9750,7 +13920,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -9768,7 +13938,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -9784,7 +13954,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -9800,7 +13970,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -9818,7 +13988,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -9834,7 +14004,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -9854,10 +14024,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="193" t="s">
+      <c r="C69" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="194"/>
+      <c r="D69" s="197"/>
       <c r="E69" s="18" t="s">
         <v>54</v>
       </c>
@@ -10229,17 +14399,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46113</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -10264,62 +14434,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -13847,7 +18017,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -13865,7 +18035,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -13881,7 +18051,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -13897,7 +18067,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -13915,7 +18085,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -13931,7 +18101,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -14326,17 +18496,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46118</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14361,62 +18531,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17912,7 +22082,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -17930,7 +22100,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -17946,7 +22116,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -17962,7 +22132,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -17980,7 +22150,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -17996,7 +22166,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -18391,17 +22561,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46120</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18426,62 +22596,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -21963,7 +26133,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -21981,7 +26151,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -21997,7 +26167,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -22013,7 +26183,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -22031,7 +26201,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -22047,7 +26217,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -22442,17 +26612,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46121</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22477,62 +26647,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -26038,7 +30208,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -26056,7 +30226,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -26072,7 +30242,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -26088,7 +30258,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -26106,7 +30276,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -26122,7 +30292,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -26517,17 +30687,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46125</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -26552,62 +30722,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="186" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -30080,7 +34250,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -30098,7 +34268,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -30114,7 +34284,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -30130,7 +34300,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -30148,7 +34318,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -30164,7 +34334,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -30559,17 +34729,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46127</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -30594,62 +34764,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34173,7 +38343,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -34191,7 +38361,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -34207,7 +38377,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -34223,7 +38393,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -34241,7 +38411,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -34257,7 +38427,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -34652,17 +38822,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46128</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -34687,62 +38857,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="195" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38258,7 +42428,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -38276,7 +42446,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -38292,7 +42462,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -38308,7 +42478,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -38326,7 +42496,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -38342,7 +42512,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
@@ -38698,7 +42868,7 @@
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" customWidth="1"/>
@@ -38737,17 +42907,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="201">
+      <c r="P1" s="204">
         <v>46129</v>
       </c>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="202"/>
-      <c r="S1" s="202"/>
-      <c r="T1" s="202"/>
-      <c r="U1" s="202"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="202"/>
-      <c r="X1" s="203"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="206"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -38772,62 +42942,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="49"/>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="208" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="208"/>
-      <c r="G4" s="209" t="s">
+      <c r="F4" s="211"/>
+      <c r="G4" s="212" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="211" t="s">
+      <c r="H4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="213" t="s">
+      <c r="I4" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="211" t="s">
+      <c r="J4" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="215" t="s">
+      <c r="L4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="216"/>
-      <c r="Q4" s="216"/>
-      <c r="R4" s="216"/>
-      <c r="S4" s="216"/>
-      <c r="T4" s="216"/>
-      <c r="U4" s="216"/>
-      <c r="V4" s="217"/>
-      <c r="W4" s="216"/>
-      <c r="X4" s="218"/>
+      <c r="M4" s="219"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="219"/>
+      <c r="T4" s="219"/>
+      <c r="U4" s="219"/>
+      <c r="V4" s="220"/>
+      <c r="W4" s="219"/>
+      <c r="X4" s="221"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="49"/>
-      <c r="B5" s="204"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="207"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="48" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="195" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="210"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="212"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="215"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38992,30 +43162,38 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="111"/>
+      <c r="C8" s="110">
+        <v>42</v>
+      </c>
+      <c r="D8" s="111">
+        <v>19</v>
+      </c>
       <c r="E8" s="112"/>
       <c r="F8" s="112"/>
-      <c r="G8" s="76"/>
+      <c r="G8" s="76">
+        <v>1</v>
+      </c>
       <c r="H8" s="73"/>
       <c r="I8" s="73">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J8" s="77">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K8" s="41"/>
       <c r="L8" s="112"/>
       <c r="M8" s="112"/>
       <c r="N8" s="112"/>
       <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
+      <c r="P8" s="112">
+        <v>1</v>
+      </c>
       <c r="Q8" s="120"/>
       <c r="R8" s="86">
         <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="124">
         <f t="shared" si="1"/>
@@ -39024,15 +43202,15 @@
       <c r="T8" s="41"/>
       <c r="U8" s="107">
         <f>L8*24+N8*24+P8*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V8" s="130">
         <f>U8/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="129">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="X8" s="27"/>
       <c r="AL8" s="12"/>
@@ -39067,7 +43245,9 @@
       <c r="B9" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="113">
+        <v>101</v>
+      </c>
       <c r="D9" s="114"/>
       <c r="E9" s="115"/>
       <c r="F9" s="115"/>
@@ -39075,7 +43255,7 @@
       <c r="H9" s="79"/>
       <c r="I9" s="78">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="J9" s="94">
         <f t="shared" si="0"/>
@@ -39107,7 +43287,7 @@
       </c>
       <c r="W9" s="133">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2424</v>
       </c>
       <c r="X9" s="52"/>
       <c r="AL9" s="12"/>
@@ -39142,15 +43322,19 @@
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="110">
+        <v>72</v>
+      </c>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="112"/>
-      <c r="G10" s="76"/>
+      <c r="G10" s="76">
+        <v>2</v>
+      </c>
       <c r="H10" s="73"/>
       <c r="I10" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J10" s="95">
         <f t="shared" si="0"/>
@@ -39159,13 +43343,17 @@
       <c r="K10" s="41"/>
       <c r="L10" s="112"/>
       <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
+      <c r="N10" s="112">
+        <v>1</v>
+      </c>
       <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
+      <c r="P10" s="112">
+        <v>1</v>
+      </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="99">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" s="126">
         <f t="shared" si="1"/>
@@ -39174,15 +43362,15 @@
       <c r="T10" s="41"/>
       <c r="U10" s="107">
         <f>L10*24+N10*24+P10*24</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="134">
         <f>U10/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="X10" s="27"/>
       <c r="AL10" s="12"/>
@@ -39292,15 +43480,19 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="110">
+        <v>5</v>
+      </c>
       <c r="D12" s="111"/>
       <c r="E12" s="112"/>
       <c r="F12" s="112"/>
-      <c r="G12" s="76"/>
+      <c r="G12" s="76">
+        <v>1</v>
+      </c>
       <c r="H12" s="73"/>
       <c r="I12" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" s="77">
         <f t="shared" si="0"/>
@@ -39309,13 +43501,15 @@
       <c r="K12" s="41"/>
       <c r="L12" s="112"/>
       <c r="M12" s="112"/>
-      <c r="N12" s="112"/>
+      <c r="N12" s="112">
+        <v>1</v>
+      </c>
       <c r="O12" s="112"/>
       <c r="P12" s="112"/>
       <c r="Q12" s="120"/>
       <c r="R12" s="86">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="124">
         <f t="shared" si="1"/>
@@ -39324,15 +43518,15 @@
       <c r="T12" s="41"/>
       <c r="U12" s="107">
         <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V12" s="130">
         <f t="shared" ref="V12:V41" si="6">U12/24</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X12" s="27"/>
       <c r="AL12" s="12"/>
@@ -39367,47 +43561,63 @@
       <c r="B13" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="C13" s="113">
+        <v>3418</v>
+      </c>
+      <c r="D13" s="114">
+        <v>14</v>
+      </c>
       <c r="E13" s="115"/>
       <c r="F13" s="115"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79"/>
+      <c r="G13" s="78">
+        <v>22</v>
+      </c>
+      <c r="H13" s="79">
+        <v>17</v>
+      </c>
       <c r="I13" s="80">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3396</v>
       </c>
       <c r="J13" s="94">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="K13" s="53"/>
       <c r="L13" s="121"/>
       <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="122"/>
+      <c r="N13" s="121">
+        <v>9</v>
+      </c>
+      <c r="O13" s="121">
+        <v>7</v>
+      </c>
+      <c r="P13" s="121">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="122">
+        <v>10</v>
+      </c>
       <c r="R13" s="97">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S13" s="125">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T13" s="53"/>
       <c r="U13" s="131">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="V13" s="135">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W13" s="133">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>81501</v>
       </c>
       <c r="X13" s="52"/>
       <c r="Y13" s="2"/>
@@ -39449,19 +43659,23 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
+      <c r="C14" s="110">
+        <v>4</v>
+      </c>
+      <c r="D14" s="111">
+        <v>16</v>
+      </c>
       <c r="E14" s="112"/>
       <c r="F14" s="112"/>
       <c r="G14" s="76"/>
       <c r="H14" s="73"/>
       <c r="I14" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" s="95">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="112"/>
@@ -39489,7 +43703,7 @@
       </c>
       <c r="W14" s="129">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="X14" s="27"/>
       <c r="AL14" s="12"/>
@@ -39524,7 +43738,9 @@
       <c r="B15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="110"/>
+      <c r="C15" s="110">
+        <v>3</v>
+      </c>
       <c r="D15" s="111"/>
       <c r="E15" s="112"/>
       <c r="F15" s="112"/>
@@ -39532,7 +43748,7 @@
       <c r="H15" s="73"/>
       <c r="I15" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="77">
         <f t="shared" si="4"/>
@@ -39564,7 +43780,7 @@
       </c>
       <c r="W15" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X15" s="27"/>
       <c r="AL15" s="12"/>
@@ -39599,7 +43815,9 @@
       <c r="B16" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="110"/>
+      <c r="C16" s="110">
+        <v>2</v>
+      </c>
       <c r="D16" s="111"/>
       <c r="E16" s="112"/>
       <c r="F16" s="112"/>
@@ -39607,7 +43825,7 @@
       <c r="H16" s="73"/>
       <c r="I16" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="77">
         <f t="shared" si="4"/>
@@ -39639,7 +43857,7 @@
       </c>
       <c r="W16" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X16" s="27"/>
       <c r="AL16" s="12"/>
@@ -39674,7 +43892,9 @@
       <c r="B17" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="110"/>
+      <c r="C17" s="110">
+        <v>1</v>
+      </c>
       <c r="D17" s="111"/>
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
@@ -39682,7 +43902,7 @@
       <c r="H17" s="73"/>
       <c r="I17" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="77">
         <f t="shared" si="4"/>
@@ -39714,7 +43934,7 @@
       </c>
       <c r="W17" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X17" s="27"/>
       <c r="AL17" s="12"/>
@@ -39749,7 +43969,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="110">
+        <v>3</v>
+      </c>
       <c r="D18" s="111"/>
       <c r="E18" s="112"/>
       <c r="F18" s="112"/>
@@ -39757,7 +43979,7 @@
       <c r="H18" s="73"/>
       <c r="I18" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" s="77">
         <f t="shared" si="4"/>
@@ -39789,7 +44011,7 @@
       </c>
       <c r="W18" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="X18" s="27"/>
       <c r="AL18" s="12"/>
@@ -39899,19 +44121,23 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="110">
+        <v>4</v>
+      </c>
+      <c r="D20" s="111">
+        <v>20</v>
+      </c>
       <c r="E20" s="112"/>
       <c r="F20" s="112"/>
       <c r="G20" s="76"/>
       <c r="H20" s="73"/>
       <c r="I20" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="112"/>
@@ -39939,7 +44165,7 @@
       </c>
       <c r="W20" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="X20" s="27"/>
       <c r="AL20" s="12"/>
@@ -39974,19 +44200,23 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="110"/>
-      <c r="D21" s="111"/>
+      <c r="C21" s="110">
+        <v>5</v>
+      </c>
+      <c r="D21" s="111">
+        <v>16</v>
+      </c>
       <c r="E21" s="112"/>
       <c r="F21" s="112"/>
       <c r="G21" s="76"/>
       <c r="H21" s="73"/>
       <c r="I21" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K21" s="41"/>
       <c r="L21" s="112"/>
@@ -40014,7 +44244,7 @@
       </c>
       <c r="W21" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X21" s="27"/>
       <c r="AL21" s="12"/>
@@ -40049,7 +44279,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="110"/>
+      <c r="C22" s="110">
+        <v>4</v>
+      </c>
       <c r="D22" s="111"/>
       <c r="E22" s="112"/>
       <c r="F22" s="112"/>
@@ -40057,7 +44289,7 @@
       <c r="H22" s="73"/>
       <c r="I22" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="77">
         <f t="shared" si="4"/>
@@ -40089,7 +44321,7 @@
       </c>
       <c r="W22" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="27"/>
       <c r="AL22" s="12"/>
@@ -40124,19 +44356,23 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="111"/>
+      <c r="C23" s="110">
+        <v>2</v>
+      </c>
+      <c r="D23" s="111">
+        <v>20</v>
+      </c>
       <c r="E23" s="112"/>
       <c r="F23" s="112"/>
       <c r="G23" s="76"/>
       <c r="H23" s="73"/>
       <c r="I23" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K23" s="42"/>
       <c r="L23" s="112"/>
@@ -40164,7 +44400,7 @@
       </c>
       <c r="W23" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="X23" s="27"/>
       <c r="Y23" s="2"/>
@@ -40206,19 +44442,23 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="110">
+        <v>37</v>
+      </c>
+      <c r="D24" s="111">
+        <v>19</v>
+      </c>
       <c r="E24" s="112"/>
       <c r="F24" s="112"/>
       <c r="G24" s="76"/>
       <c r="H24" s="73"/>
       <c r="I24" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J24" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K24" s="42"/>
       <c r="L24" s="112"/>
@@ -40246,7 +44486,7 @@
       </c>
       <c r="W24" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="X24" s="27"/>
       <c r="Y24" s="2"/>
@@ -40288,7 +44528,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="110"/>
+      <c r="C25" s="110">
+        <v>11</v>
+      </c>
       <c r="D25" s="111"/>
       <c r="E25" s="112"/>
       <c r="F25" s="112"/>
@@ -40296,7 +44538,7 @@
       <c r="H25" s="73"/>
       <c r="I25" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J25" s="77">
         <f t="shared" si="4"/>
@@ -40328,7 +44570,7 @@
       </c>
       <c r="W25" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="X25" s="27"/>
       <c r="AL25" s="12"/>
@@ -40363,19 +44605,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="110"/>
-      <c r="D26" s="111"/>
+      <c r="C26" s="110">
+        <v>3</v>
+      </c>
+      <c r="D26" s="111">
+        <v>1</v>
+      </c>
       <c r="E26" s="112"/>
       <c r="F26" s="112"/>
       <c r="G26" s="76"/>
       <c r="H26" s="73"/>
       <c r="I26" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="41"/>
       <c r="L26" s="112"/>
@@ -40403,7 +44649,7 @@
       </c>
       <c r="W26" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="X26" s="27"/>
       <c r="BE26" s="14" t="e">
@@ -40419,7 +44665,9 @@
       <c r="B27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="110"/>
+      <c r="C27" s="110">
+        <v>6</v>
+      </c>
       <c r="D27" s="111"/>
       <c r="E27" s="112"/>
       <c r="F27" s="112"/>
@@ -40427,7 +44675,7 @@
       <c r="H27" s="73"/>
       <c r="I27" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J27" s="77">
         <f t="shared" si="4"/>
@@ -40459,7 +44707,7 @@
       </c>
       <c r="W27" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X27" s="27"/>
       <c r="Y27" s="2"/>
@@ -40478,7 +44726,9 @@
       <c r="B28" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="110"/>
+      <c r="C28" s="110">
+        <v>4</v>
+      </c>
       <c r="D28" s="111"/>
       <c r="E28" s="112"/>
       <c r="F28" s="112"/>
@@ -40486,7 +44736,7 @@
       <c r="H28" s="73"/>
       <c r="I28" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="77">
         <f t="shared" si="4"/>
@@ -40518,7 +44768,7 @@
       </c>
       <c r="W28" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X28" s="27"/>
       <c r="Y28" s="2"/>
@@ -40596,15 +44846,19 @@
       <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="110"/>
+      <c r="C30" s="110">
+        <v>60</v>
+      </c>
       <c r="D30" s="111"/>
       <c r="E30" s="112"/>
       <c r="F30" s="112"/>
-      <c r="G30" s="76"/>
+      <c r="G30" s="76">
+        <v>3</v>
+      </c>
       <c r="H30" s="73"/>
       <c r="I30" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J30" s="77">
         <f t="shared" si="4"/>
@@ -40613,13 +44867,17 @@
       <c r="K30" s="41"/>
       <c r="L30" s="112"/>
       <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
+      <c r="N30" s="112">
+        <v>1</v>
+      </c>
       <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
+      <c r="P30" s="112">
+        <v>2</v>
+      </c>
       <c r="Q30" s="120"/>
       <c r="R30" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S30" s="124">
         <f t="shared" si="7"/>
@@ -40628,15 +44886,15 @@
       <c r="T30" s="41"/>
       <c r="U30" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V30" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="X30" s="27"/>
     </row>
@@ -40648,15 +44906,19 @@
       <c r="B31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="110">
+        <v>35</v>
+      </c>
       <c r="D31" s="111"/>
       <c r="E31" s="112"/>
       <c r="F31" s="112"/>
-      <c r="G31" s="76"/>
+      <c r="G31" s="76">
+        <v>1</v>
+      </c>
       <c r="H31" s="73"/>
       <c r="I31" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J31" s="77">
         <f t="shared" si="4"/>
@@ -40667,11 +44929,13 @@
       <c r="M31" s="112"/>
       <c r="N31" s="112"/>
       <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
+      <c r="P31" s="112">
+        <v>1</v>
+      </c>
       <c r="Q31" s="120"/>
       <c r="R31" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="124">
         <f t="shared" si="7"/>
@@ -40680,15 +44944,15 @@
       <c r="T31" s="41"/>
       <c r="U31" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="X31" s="27"/>
     </row>
@@ -40752,7 +45016,9 @@
       <c r="B33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="110"/>
+      <c r="C33" s="110">
+        <v>2</v>
+      </c>
       <c r="D33" s="111"/>
       <c r="E33" s="112"/>
       <c r="F33" s="112"/>
@@ -40760,7 +45026,7 @@
       <c r="H33" s="73"/>
       <c r="I33" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="77">
         <f t="shared" si="4"/>
@@ -40792,7 +45058,7 @@
       </c>
       <c r="W33" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X33" s="27"/>
     </row>
@@ -40804,7 +45070,9 @@
       <c r="B34" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="110"/>
+      <c r="C34" s="110">
+        <v>4</v>
+      </c>
       <c r="D34" s="111"/>
       <c r="E34" s="112"/>
       <c r="F34" s="112"/>
@@ -40812,7 +45080,7 @@
       <c r="H34" s="73"/>
       <c r="I34" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J34" s="77">
         <f t="shared" si="4"/>
@@ -40844,7 +45112,7 @@
       </c>
       <c r="W34" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X34" s="27"/>
     </row>
@@ -40856,30 +45124,38 @@
       <c r="B35" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
+      <c r="C35" s="110">
+        <v>95</v>
+      </c>
+      <c r="D35" s="111">
+        <v>1</v>
+      </c>
       <c r="E35" s="112"/>
       <c r="F35" s="112"/>
-      <c r="G35" s="76"/>
+      <c r="G35" s="76">
+        <v>1</v>
+      </c>
       <c r="H35" s="73"/>
       <c r="I35" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J35" s="77">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="112"/>
       <c r="M35" s="112"/>
       <c r="N35" s="112"/>
       <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
+      <c r="P35" s="112">
+        <v>1</v>
+      </c>
       <c r="Q35" s="120"/>
       <c r="R35" s="86">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="124">
         <f t="shared" si="7"/>
@@ -40888,15 +45164,15 @@
       <c r="T35" s="41"/>
       <c r="U35" s="107">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V35" s="130">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2257</v>
       </c>
       <c r="X35" s="27"/>
     </row>
@@ -40960,7 +45236,9 @@
       <c r="B37" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="110">
+        <v>2</v>
+      </c>
       <c r="D37" s="111"/>
       <c r="E37" s="112"/>
       <c r="F37" s="112"/>
@@ -40968,7 +45246,7 @@
       <c r="H37" s="73"/>
       <c r="I37" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="77">
         <f t="shared" si="4"/>
@@ -41000,7 +45278,7 @@
       </c>
       <c r="W37" s="129">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X37" s="27"/>
     </row>
@@ -41012,30 +45290,40 @@
       <c r="B38" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="113"/>
-      <c r="D38" s="114"/>
+      <c r="C38" s="113">
+        <v>3282</v>
+      </c>
+      <c r="D38" s="114">
+        <v>2</v>
+      </c>
       <c r="E38" s="115"/>
       <c r="F38" s="115"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="78">
+        <v>43</v>
+      </c>
       <c r="H38" s="79"/>
       <c r="I38" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3239</v>
       </c>
       <c r="J38" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" s="51"/>
       <c r="L38" s="121"/>
       <c r="M38" s="121"/>
-      <c r="N38" s="121"/>
+      <c r="N38" s="121">
+        <v>28</v>
+      </c>
       <c r="O38" s="121"/>
-      <c r="P38" s="121"/>
+      <c r="P38" s="121">
+        <v>15</v>
+      </c>
       <c r="Q38" s="122"/>
       <c r="R38" s="97">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S38" s="125">
         <f t="shared" si="7"/>
@@ -41044,15 +45332,15 @@
       <c r="T38" s="51"/>
       <c r="U38" s="131">
         <f>L38*6+N38*6+P38*6</f>
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="V38" s="135">
         <f>U38/6</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="W38" s="133">
         <f>I38*6+J38</f>
-        <v>0</v>
+        <v>19436</v>
       </c>
       <c r="X38" s="52"/>
     </row>
@@ -41064,7 +45352,9 @@
       <c r="B39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="110"/>
+      <c r="C39" s="110">
+        <v>7</v>
+      </c>
       <c r="D39" s="111"/>
       <c r="E39" s="112"/>
       <c r="F39" s="112"/>
@@ -41072,7 +45362,7 @@
       <c r="H39" s="73"/>
       <c r="I39" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" s="77">
         <f t="shared" si="4"/>
@@ -41104,7 +45394,7 @@
       </c>
       <c r="W39" s="129">
         <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X39" s="27"/>
     </row>
@@ -41116,7 +45406,9 @@
       <c r="B40" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="116">
+        <v>4</v>
+      </c>
       <c r="D40" s="117"/>
       <c r="E40" s="118"/>
       <c r="F40" s="118"/>
@@ -41124,7 +45416,7 @@
       <c r="H40" s="80"/>
       <c r="I40" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="77">
         <f t="shared" si="4"/>
@@ -41156,7 +45448,7 @@
       </c>
       <c r="W40" s="137">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X40" s="92"/>
     </row>
@@ -41168,30 +45460,38 @@
       <c r="B41" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="146"/>
-      <c r="D41" s="147"/>
+      <c r="C41" s="146">
+        <v>253</v>
+      </c>
+      <c r="D41" s="147">
+        <v>20</v>
+      </c>
       <c r="E41" s="148"/>
       <c r="F41" s="148"/>
-      <c r="G41" s="149"/>
+      <c r="G41" s="149">
+        <v>2</v>
+      </c>
       <c r="H41" s="150"/>
       <c r="I41" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="J41" s="152">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" s="153"/>
       <c r="L41" s="154"/>
       <c r="M41" s="154"/>
       <c r="N41" s="154"/>
       <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
+      <c r="P41" s="154">
+        <v>2</v>
+      </c>
       <c r="Q41" s="155"/>
       <c r="R41" s="156">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S41" s="157">
         <f t="shared" si="7"/>
@@ -41200,15 +45500,15 @@
       <c r="T41" s="153"/>
       <c r="U41" s="158">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V41" s="159">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" s="159">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6044</v>
       </c>
       <c r="X41" s="160"/>
     </row>
@@ -41220,15 +45520,19 @@
       <c r="B42" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="163">
+        <v>828</v>
+      </c>
       <c r="D42" s="164"/>
       <c r="E42" s="165"/>
       <c r="F42" s="165"/>
-      <c r="G42" s="166"/>
+      <c r="G42" s="166">
+        <v>22</v>
+      </c>
       <c r="H42" s="167"/>
       <c r="I42" s="166">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="J42" s="168">
         <f t="shared" si="4"/>
@@ -41237,13 +45541,17 @@
       <c r="K42" s="169"/>
       <c r="L42" s="165"/>
       <c r="M42" s="165"/>
-      <c r="N42" s="165"/>
+      <c r="N42" s="165">
+        <v>2</v>
+      </c>
       <c r="O42" s="165"/>
-      <c r="P42" s="165"/>
+      <c r="P42" s="165">
+        <v>20</v>
+      </c>
       <c r="Q42" s="170"/>
       <c r="R42" s="171">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S42" s="172">
         <f t="shared" si="7"/>
@@ -41252,15 +45560,15 @@
       <c r="T42" s="169"/>
       <c r="U42" s="173">
         <f>L42*12+N42*12+P42*12</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V42" s="174">
         <f>U42/12</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W42" s="175">
         <f>I42*12+J42</f>
-        <v>0</v>
+        <v>9672</v>
       </c>
       <c r="X42" s="176"/>
     </row>
@@ -41315,30 +45623,40 @@
       <c r="B44" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="113"/>
-      <c r="D44" s="114"/>
+      <c r="C44" s="113">
+        <v>22777</v>
+      </c>
+      <c r="D44" s="114">
+        <v>5</v>
+      </c>
       <c r="E44" s="115"/>
       <c r="F44" s="115"/>
-      <c r="G44" s="78"/>
+      <c r="G44" s="78">
+        <v>856</v>
+      </c>
       <c r="H44" s="79"/>
       <c r="I44" s="73">
         <f>C44+E44-G44</f>
-        <v>0</v>
+        <v>21921</v>
       </c>
       <c r="J44" s="177">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K44" s="51"/>
       <c r="L44" s="121"/>
       <c r="M44" s="121"/>
-      <c r="N44" s="121"/>
+      <c r="N44" s="121">
+        <v>325</v>
+      </c>
       <c r="O44" s="121"/>
-      <c r="P44" s="121"/>
+      <c r="P44" s="121">
+        <v>531</v>
+      </c>
       <c r="Q44" s="122"/>
       <c r="R44" s="178">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="S44" s="179">
         <f t="shared" si="7"/>
@@ -41347,15 +45665,15 @@
       <c r="T44" s="51"/>
       <c r="U44" s="131">
         <f>L44*6+N44*6+P44*6</f>
-        <v>0</v>
+        <v>5136</v>
       </c>
       <c r="V44" s="130">
         <f>U44/6</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="W44" s="133">
         <f>I44*6+J44</f>
-        <v>0</v>
+        <v>131531</v>
       </c>
       <c r="X44" s="52"/>
       <c r="Z44" s="47"/>
@@ -41515,19 +45833,23 @@
       <c r="B48" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="142"/>
+      <c r="C48" s="141">
+        <v>2830</v>
+      </c>
+      <c r="D48" s="142">
+        <v>4</v>
+      </c>
       <c r="E48" s="121"/>
       <c r="F48" s="121"/>
       <c r="G48" s="143"/>
       <c r="H48" s="139"/>
       <c r="I48" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2830</v>
       </c>
       <c r="J48" s="140">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" s="51"/>
       <c r="L48" s="121"/>
@@ -41555,7 +45877,7 @@
       </c>
       <c r="W48" s="133">
         <f>I48*6+J48</f>
-        <v>0</v>
+        <v>16984</v>
       </c>
       <c r="X48" s="52"/>
     </row>
@@ -41567,7 +45889,9 @@
       <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="110"/>
+      <c r="C49" s="110">
+        <v>1</v>
+      </c>
       <c r="D49" s="111"/>
       <c r="E49" s="112"/>
       <c r="F49" s="112"/>
@@ -41575,7 +45899,7 @@
       <c r="H49" s="73"/>
       <c r="I49" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="77">
         <f t="shared" si="4"/>
@@ -41607,7 +45931,7 @@
       </c>
       <c r="W49" s="129">
         <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X49" s="27"/>
     </row>
@@ -41619,7 +45943,9 @@
       <c r="B50" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="110"/>
+      <c r="C50" s="110">
+        <v>4</v>
+      </c>
       <c r="D50" s="111"/>
       <c r="E50" s="112"/>
       <c r="F50" s="112"/>
@@ -41627,7 +45953,7 @@
       <c r="H50" s="73"/>
       <c r="I50" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J50" s="77">
         <f t="shared" si="4"/>
@@ -41659,7 +45985,7 @@
       </c>
       <c r="W50" s="129">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X50" s="27"/>
     </row>
@@ -41723,7 +46049,9 @@
       <c r="B52" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="141"/>
+      <c r="C52" s="141">
+        <v>34</v>
+      </c>
       <c r="D52" s="142"/>
       <c r="E52" s="121"/>
       <c r="F52" s="121"/>
@@ -41731,7 +46059,7 @@
       <c r="H52" s="139"/>
       <c r="I52" s="139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J52" s="140">
         <f t="shared" si="4"/>
@@ -41763,7 +46091,7 @@
       </c>
       <c r="W52" s="133">
         <f>I52*6+J52</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="X52" s="52"/>
     </row>
@@ -41775,7 +46103,9 @@
       <c r="B53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="110"/>
+      <c r="C53" s="110">
+        <v>2</v>
+      </c>
       <c r="D53" s="111"/>
       <c r="E53" s="112"/>
       <c r="F53" s="112"/>
@@ -41783,7 +46113,7 @@
       <c r="H53" s="73"/>
       <c r="I53" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" s="77">
         <f t="shared" si="4"/>
@@ -41815,7 +46145,7 @@
       </c>
       <c r="W53" s="129">
         <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X53" s="27"/>
     </row>
@@ -41827,7 +46157,9 @@
       <c r="B54" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="110"/>
+      <c r="C54" s="110">
+        <v>14</v>
+      </c>
       <c r="D54" s="111"/>
       <c r="E54" s="112"/>
       <c r="F54" s="112"/>
@@ -41835,7 +46167,7 @@
       <c r="H54" s="73"/>
       <c r="I54" s="73">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="77">
         <f t="shared" si="4"/>
@@ -41867,7 +46199,7 @@
       </c>
       <c r="W54" s="129">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X54" s="27"/>
     </row>
@@ -42082,11 +46414,11 @@
       </c>
       <c r="C60" s="43">
         <f>SUM(C8:C59)</f>
-        <v>0</v>
+        <v>33961</v>
       </c>
       <c r="D60" s="54">
         <f>SUM(D8:D59)</f>
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="E60" s="44">
         <f>SUM(E8:E59)</f>
@@ -42095,19 +46427,19 @@
       <c r="F60" s="44"/>
       <c r="G60" s="28">
         <f>SUM(G8:G59)</f>
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="H60" s="56">
         <f>SUM(H8:H59)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I60" s="56">
         <f>SUM(I8:I59)</f>
-        <v>0</v>
+        <v>33007</v>
       </c>
       <c r="J60" s="45">
         <f>SUM(J8:J59)</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="K60" s="46"/>
       <c r="L60" s="74">
@@ -42120,40 +46452,40 @@
       </c>
       <c r="N60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="O60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P60" s="74">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="Q60" s="75">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R60" s="85">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="S60" s="84">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T60" s="46"/>
       <c r="U60" s="43">
         <f>SUM(U8:U59)</f>
-        <v>0</v>
+        <v>6450</v>
       </c>
       <c r="V60" s="102">
         <f>SUM(V8:V59)</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="90">
+        <v>954</v>
+      </c>
+      <c r="W60" s="180">
         <f>SUM(W8:W59)</f>
-        <v>0</v>
+        <v>278204</v>
       </c>
       <c r="X60" s="45"/>
     </row>
@@ -42161,7 +46493,7 @@
       <c r="V61" s="103"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="196" t="s">
+      <c r="G62" s="199" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="57"/>
@@ -42179,7 +46511,7 @@
       <c r="S62" s="32"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="197"/>
+      <c r="G63" s="200"/>
       <c r="H63" s="58"/>
       <c r="I63" s="58"/>
       <c r="J63" s="24" t="s">
@@ -42195,7 +46527,7 @@
       <c r="S63" s="35"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="198"/>
+      <c r="G64" s="201"/>
       <c r="H64" s="59"/>
       <c r="I64" s="59"/>
       <c r="J64" s="24" t="s">
@@ -42211,7 +46543,7 @@
       <c r="S64" s="38"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="202" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="60"/>
@@ -42229,7 +46561,7 @@
       <c r="S65" s="38"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="199"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="60"/>
       <c r="I66" s="60"/>
       <c r="J66" s="24" t="s">
@@ -42245,7 +46577,7 @@
       <c r="S66" s="35"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="200"/>
+      <c r="G67" s="203"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="25" t="s">
